--- a/data/rateBuildUp/File1/RPT_RPT8270621607594XL_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT8270621607594XL_rateBuildUp.xlsx
@@ -3161,7 +3161,7 @@
         <v>13592367.50063526</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>15339904.73168357</v>
+        <v>15339904.73168356</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>17813098.7819269</v>
@@ -3170,49 +3170,49 @@
         <v>19768844.02799102</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>221.0360737948077</v>
+        <v>221.0360737948076</v>
       </c>
       <c r="BY11" s="372" t="n">
-        <v>256.0373391449633</v>
+        <v>256.0373391449632</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>290.7627916682948</v>
+        <v>290.7627916682947</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>319.991144795821</v>
+        <v>319.9911447958209</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>341.4154535024091</v>
+        <v>341.415453502409</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>40.716492655001</v>
+        <v>40.71649265500098</v>
       </c>
       <c r="CD11" s="389" t="n">
-        <v>45.37142555087766</v>
+        <v>45.37142555087765</v>
       </c>
       <c r="CE11" s="389" t="n">
-        <v>50.56632045713852</v>
+        <v>50.5663204571385</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>57.96316650475859</v>
+        <v>57.96316650475856</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>63.22722425690537</v>
+        <v>63.22722425690534</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>0.319508102201894</v>
+        <v>0.3195081022019792</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>0.3154593681255733</v>
+        <v>0.3154593681256301</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>0.3878046241620154</v>
+        <v>0.3878046241621291</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>0.4341048751705898</v>
+        <v>0.4341048751707035</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>0.4981780291967652</v>
+        <v>0.4981780291968789</v>
       </c>
       <c r="DC11" s="393" t="n">
         <v>0.003663243199316664</v>
@@ -3221,10 +3221,10 @@
         <v>0.002417437258650395</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.002554958909242371</v>
+        <v>0.002554958909242372</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.002648518712690636</v>
+        <v>0.002648518712690635</v>
       </c>
       <c r="DG11" s="395" t="n">
         <v>0.002845987409583391</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="BS12" s="391" t="n">
-        <v>6692886.60570795</v>
+        <v>6692886.605707948</v>
       </c>
       <c r="BT12" s="375" t="n">
-        <v>6269230.880298923</v>
+        <v>6269230.880298922</v>
       </c>
       <c r="BU12" s="375" t="n">
         <v>6914963.558694161</v>
@@ -3452,7 +3452,7 @@
         <v>8907633.791934106</v>
       </c>
       <c r="BX12" s="386" t="n">
-        <v>300.077895273195</v>
+        <v>300.0778952731949</v>
       </c>
       <c r="BY12" s="372" t="n">
         <v>344.5819267028969</v>
@@ -3467,7 +3467,7 @@
         <v>481.6271647332809</v>
       </c>
       <c r="CC12" s="386" t="n">
-        <v>24.667889004872</v>
+        <v>24.66788900487199</v>
       </c>
       <c r="CD12" s="372" t="n">
         <v>22.92204977440284</v>
@@ -3482,22 +3482,22 @@
         <v>31.8016994595361</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>1.389209119547729</v>
+        <v>1.389209119547786</v>
       </c>
       <c r="CX12" s="103" t="n">
-        <v>0.8222749890064733</v>
+        <v>0.8222749890065302</v>
       </c>
       <c r="CY12" s="103" t="n">
         <v>1.194036024692821</v>
       </c>
       <c r="CZ12" s="103" t="n">
-        <v>1.394814763450881</v>
+        <v>1.394814763450938</v>
       </c>
       <c r="DA12" s="104" t="n">
         <v>1.584244824146481</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.006531473728361525</v>
+        <v>0.006531473728361528</v>
       </c>
       <c r="DD12" s="397" t="n">
         <v>0.002519340210384256</v>
@@ -3506,7 +3506,7 @@
         <v>0.002807067274393979</v>
       </c>
       <c r="DF12" s="397" t="n">
-        <v>0.003000901322391394</v>
+        <v>0.003000901322391395</v>
       </c>
       <c r="DG12" s="398" t="n">
         <v>0.003316664815969999</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>7428443.884957647</v>
+        <v>7428443.884957645</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>8649579.032607021</v>
+        <v>8649579.032607019</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>9011950.216916285</v>
+        <v>9011950.216916284</v>
       </c>
       <c r="BV14" s="420" t="n">
         <v>10672385.86352629</v>
@@ -4016,49 +4016,49 @@
         <v>12712332.24587731</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>921.4658679731419</v>
+        <v>921.4658679731416</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>951.5996717218443</v>
+        <v>951.5996717218441</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>879.1789239242275</v>
+        <v>879.1789239242274</v>
       </c>
       <c r="CA14" s="417" t="n">
         <v>918.7940300041739</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>959.4808656089658</v>
+        <v>959.4808656089655</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>806.2420611814094</v>
+        <v>806.2420611814091</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>837.7250044033194</v>
+        <v>837.7250044033193</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>774.6322467715247</v>
+        <v>774.6322467715246</v>
       </c>
       <c r="CF14" s="417" t="n">
         <v>815.0399238435808</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>858.8082854118504</v>
+        <v>858.8082854118502</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>64.96387344628249</v>
+        <v>64.96387344628283</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>66.00920127642053</v>
+        <v>66.00920127642075</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>67.82567766326349</v>
+        <v>67.8256776632636</v>
       </c>
       <c r="CZ14" s="133" t="n">
         <v>69.04872982940196</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>70.45561905760928</v>
+        <v>70.45561905760962</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0.1008406183369965</v>
@@ -4283,49 +4283,49 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>26356373.57329554</v>
+        <v>26356373.57329553</v>
       </c>
       <c r="BT15" s="440" t="n">
         <v>28709179.20304899</v>
       </c>
       <c r="BU15" s="440" t="n">
-        <v>31488911.90547825</v>
+        <v>31488911.90547824</v>
       </c>
       <c r="BV15" s="440" t="n">
-        <v>36767856.60592004</v>
+        <v>36767856.60592003</v>
       </c>
       <c r="BW15" s="441" t="n">
-        <v>41704551.57206431</v>
+        <v>41704551.5720643</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>309.3136892127146</v>
+        <v>309.3136892127145</v>
       </c>
       <c r="BY15" s="443" t="n">
         <v>355.8080302137848</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>395.0354675142579</v>
+        <v>395.0354675142578</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>432.9675524016264</v>
+        <v>432.9675524016263</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>463.3059453378227</v>
+        <v>463.3059453378225</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>45.39885012720889</v>
+        <v>45.39885012720887</v>
       </c>
       <c r="CD15" s="443" t="n">
         <v>48.84938984094185</v>
       </c>
       <c r="CE15" s="443" t="n">
-        <v>52.9261209405287</v>
+        <v>52.92612094052869</v>
       </c>
       <c r="CF15" s="443" t="n">
-        <v>61.04287458219935</v>
+        <v>61.04287458219934</v>
       </c>
       <c r="CG15" s="444" t="n">
-        <v>68.14402902997155</v>
+        <v>68.14402902997153</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -7336,64 +7336,64 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>24419.77128613649</v>
+        <v>24419.77128613648</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>3512.981078027557</v>
       </c>
       <c r="BU29" s="375" t="n">
-        <v>2768.053604727735</v>
+        <v>2768.053604727734</v>
       </c>
       <c r="BV29" s="375" t="n">
-        <v>2010.698402382618</v>
+        <v>2010.698402382617</v>
       </c>
       <c r="BW29" s="392" t="n">
-        <v>1245.763044370075</v>
+        <v>1245.763044370074</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.448222479721036</v>
+        <v>0.4482224797210358</v>
       </c>
       <c r="BY29" s="372" t="n">
-        <v>0.0661734850564291</v>
+        <v>0.06617348505642909</v>
       </c>
       <c r="BZ29" s="372" t="n">
-        <v>0.05246753533845386</v>
+        <v>0.05246753533845384</v>
       </c>
       <c r="CA29" s="372" t="n">
-        <v>0.03611980663748068</v>
+        <v>0.03611980663748066</v>
       </c>
       <c r="CB29" s="387" t="n">
-        <v>0.02151480147994134</v>
+        <v>0.02151480147994133</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.08256592234039495</v>
+        <v>0.08256592234039492</v>
       </c>
       <c r="CD29" s="389" t="n">
         <v>0.01172635741609546</v>
       </c>
       <c r="CE29" s="389" t="n">
-        <v>0.009124586369177422</v>
+        <v>0.009124586369177418</v>
       </c>
       <c r="CF29" s="389" t="n">
-        <v>0.006542738448540089</v>
+        <v>0.006542738448540086</v>
       </c>
       <c r="CG29" s="390" t="n">
-        <v>0.003984357368889431</v>
+        <v>0.003984357368889429</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>0.01785595839983961</v>
+        <v>0.01785595839983972</v>
       </c>
       <c r="CX29" s="92" t="n">
-        <v>0.0005242751429811315</v>
+        <v>0.0005242751429811454</v>
       </c>
       <c r="CY29" s="92" t="n">
-        <v>0.0004095334412153179</v>
+        <v>0.0004095334412153387</v>
       </c>
       <c r="CZ29" s="92" t="n">
-        <v>0.0002741183982437612</v>
+        <v>0.000274118398243775</v>
       </c>
       <c r="DA29" s="93" t="n">
-        <v>0.000154024023518988</v>
+        <v>0.0001540240235189949</v>
       </c>
       <c r="DC29" s="393" t="n">
         <v>0.04044892817483209</v>
@@ -7621,7 +7621,7 @@
         <v>34870.49269478698</v>
       </c>
       <c r="BT30" s="375" t="n">
-        <v>535.0111726461538</v>
+        <v>535.0111726461537</v>
       </c>
       <c r="BU30" s="375" t="n">
         <v>421.8956008204515</v>
@@ -7639,7 +7639,7 @@
         <v>0.02940634731723226</v>
       </c>
       <c r="BZ30" s="372" t="n">
-        <v>0.02572933705455119</v>
+        <v>0.02572933705455118</v>
       </c>
       <c r="CA30" s="372" t="n">
         <v>0.01783692681688848</v>
@@ -7651,7 +7651,7 @@
         <v>0.1285217416662355</v>
       </c>
       <c r="CD30" s="372" t="n">
-        <v>0.00195614948044026</v>
+        <v>0.001956149480440259</v>
       </c>
       <c r="CE30" s="372" t="n">
         <v>0.001530714831127044</v>
@@ -7660,22 +7660,22 @@
         <v>0.001112151418622067</v>
       </c>
       <c r="CG30" s="387" t="n">
-        <v>0.0006921598570196272</v>
+        <v>0.0006921598570196271</v>
       </c>
       <c r="CW30" s="102" t="n">
         <v>0.07077391152844092</v>
       </c>
       <c r="CX30" s="103" t="n">
-        <v>0.0002842418608596207</v>
+        <v>0.0002842418608596277</v>
       </c>
       <c r="CY30" s="103" t="n">
-        <v>0.0002500499428132082</v>
+        <v>0.0002500499428132116</v>
       </c>
       <c r="CZ30" s="103" t="n">
         <v>0.0001695215325657543</v>
       </c>
       <c r="DA30" s="104" t="n">
-        <v>9.430141899412388e-05</v>
+        <v>9.430141899412561e-05</v>
       </c>
       <c r="DC30" s="396" t="n">
         <v>0.0451564015983103</v>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="BS32" s="419" t="n">
-        <v>18889.36835995101</v>
+        <v>18889.368359951</v>
       </c>
       <c r="BT32" s="420" t="n">
-        <v>66.64626502818014</v>
+        <v>66.64626502818012</v>
       </c>
       <c r="BU32" s="420" t="n">
         <v>0</v>
@@ -8197,10 +8197,10 @@
         <v>0</v>
       </c>
       <c r="BX32" s="416" t="n">
-        <v>2.343143258645737</v>
+        <v>2.343143258645736</v>
       </c>
       <c r="BY32" s="417" t="n">
-        <v>0.007332213935871515</v>
+        <v>0.007332213935871513</v>
       </c>
       <c r="BZ32" s="417" t="n">
         <v>0</v>
@@ -8212,10 +8212,10 @@
         <v>0</v>
       </c>
       <c r="CC32" s="417" t="n">
-        <v>2.05014717978564</v>
+        <v>2.050147179785639</v>
       </c>
       <c r="CD32" s="417" t="n">
-        <v>0.006454793054520391</v>
+        <v>0.006454793054520389</v>
       </c>
       <c r="CE32" s="417" t="n">
         <v>0</v>
@@ -8227,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="CW32" s="132" t="n">
-        <v>0.002828538497753108</v>
+        <v>0.002828538497753996</v>
       </c>
       <c r="CX32" s="133" t="n">
-        <v>0.0004630348066374671</v>
+        <v>0.0004630348066374688</v>
       </c>
       <c r="CY32" s="133" t="n">
         <v>0</v>
@@ -8467,10 +8467,10 @@
         <v>79083.85202267645</v>
       </c>
       <c r="BT33" s="440" t="n">
-        <v>4114.747423712415</v>
+        <v>4114.747423712414</v>
       </c>
       <c r="BU33" s="440" t="n">
-        <v>3190.050053885117</v>
+        <v>3190.050053885116</v>
       </c>
       <c r="BV33" s="440" t="n">
         <v>2319.448089110551</v>
@@ -8485,7 +8485,7 @@
         <v>0.05099623940146895</v>
       </c>
       <c r="BZ33" s="443" t="n">
-        <v>0.04001989393006469</v>
+        <v>0.04001989393006468</v>
       </c>
       <c r="CA33" s="443" t="n">
         <v>0.0273131440004346</v>
@@ -8497,16 +8497,16 @@
         <v>0.1362219250488082</v>
       </c>
       <c r="CD33" s="443" t="n">
-        <v>0.007001346140073273</v>
+        <v>0.007001346140073271</v>
       </c>
       <c r="CE33" s="443" t="n">
-        <v>0.005361791333567501</v>
+        <v>0.005361791333567499</v>
       </c>
       <c r="CF33" s="443" t="n">
-        <v>0.003850803170851695</v>
+        <v>0.003850803170851694</v>
       </c>
       <c r="CG33" s="444" t="n">
-        <v>0.002352466238998582</v>
+        <v>0.002352466238998581</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" thickBot="1">
@@ -9426,19 +9426,19 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>61232.73873833254</v>
+        <v>61232.73873833253</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>56949.0960418696</v>
+        <v>56949.09604186958</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>71170.91319251488</v>
+        <v>71170.91319251485</v>
       </c>
       <c r="BV38" s="375" t="n">
-        <v>37489.11030063114</v>
+        <v>37489.11030063112</v>
       </c>
       <c r="BW38" s="392" t="n">
-        <v>40410.4627293431</v>
+        <v>40410.46272934308</v>
       </c>
       <c r="BX38" s="386" t="n">
         <v>1.123920845769233</v>
@@ -9447,13 +9447,13 @@
         <v>1.072741376113453</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>1.349020985944959</v>
+        <v>1.349020985944958</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.6734473024225881</v>
+        <v>0.6734473024225879</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.6979040574879253</v>
+        <v>0.6979040574879249</v>
       </c>
       <c r="CC38" s="388" t="n">
         <v>0.2070345988141619</v>
@@ -9462,7 +9462,7 @@
         <v>0.1900965134390831</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.2346071417436318</v>
+        <v>0.2346071417436317</v>
       </c>
       <c r="CF38" s="389" t="n">
         <v>0.1219881823523848</v>
@@ -9471,19 +9471,19 @@
         <v>0.1292458671683467</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>0.02017955311891884</v>
+        <v>0.02017955311891906</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>0.001211920784345066</v>
+        <v>0.001211920784345288</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>0.00154298261871344</v>
+        <v>0.001542982618713884</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>0.002607978788935483</v>
+        <v>0.002607978788935705</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>0.00307357056153601</v>
+        <v>0.003073570561536343</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0.01982174819731641</v>
@@ -9492,7 +9492,7 @@
         <v>0.002315458233581055</v>
       </c>
       <c r="DE38" s="394" t="n">
-        <v>0.002365691163292893</v>
+        <v>0.002365691163292892</v>
       </c>
       <c r="DF38" s="394" t="n">
         <v>0.005148140219367031</v>
@@ -9714,7 +9714,7 @@
         <v>50372.41274585562</v>
       </c>
       <c r="BU39" s="375" t="n">
-        <v>65154.34859173407</v>
+        <v>65154.34859173406</v>
       </c>
       <c r="BV39" s="375" t="n">
         <v>14043.57906633647</v>
@@ -9732,7 +9732,7 @@
         <v>3.973443174630005</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>0.8115646454014094</v>
+        <v>0.8115646454014093</v>
       </c>
       <c r="CB39" s="387" t="n">
         <v>0.8946734527412963</v>
@@ -9744,25 +9744,25 @@
         <v>0.1841755351275582</v>
       </c>
       <c r="CE39" s="372" t="n">
-        <v>0.236391959308987</v>
+        <v>0.2363919593089869</v>
       </c>
       <c r="CF39" s="372" t="n">
-        <v>0.05060192156151602</v>
+        <v>0.05060192156151601</v>
       </c>
       <c r="CG39" s="387" t="n">
         <v>0.0590750238813058</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.06198481306400749</v>
+        <v>0.06198481306400794</v>
       </c>
       <c r="CX39" s="103" t="n">
         <v>0.0006432358254646608</v>
       </c>
       <c r="CY39" s="103" t="n">
-        <v>0.001510474575277865</v>
+        <v>0.001510474575278309</v>
       </c>
       <c r="CZ39" s="103" t="n">
-        <v>0.001267832343081254</v>
+        <v>0.001267832343081365</v>
       </c>
       <c r="DA39" s="104" t="n">
         <v>0.001372429611141257</v>
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>432172.2644007935</v>
+        <v>432172.2644007934</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>614687.7416411932</v>
+        <v>614687.741641193</v>
       </c>
       <c r="BU41" s="420" t="n">
         <v>198157.6575402865</v>
@@ -10284,31 +10284,31 @@
         <v>243364.0560568464</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>299695.0017220364</v>
+        <v>299695.0017220363</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>53.60907303027515</v>
+        <v>53.60907303027513</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>67.6260256079652</v>
+        <v>67.62602560796519</v>
       </c>
       <c r="BZ41" s="417" t="n">
-        <v>19.33166872100499</v>
+        <v>19.33166872100498</v>
       </c>
       <c r="CA41" s="417" t="n">
         <v>20.95140155930896</v>
       </c>
       <c r="CB41" s="418" t="n">
-        <v>22.61989492637709</v>
+        <v>22.61989492637708</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>46.90557842693045</v>
+        <v>46.90557842693043</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>59.53345118089869</v>
+        <v>59.53345118089868</v>
       </c>
       <c r="CE41" s="417" t="n">
-        <v>17.03286278560236</v>
+        <v>17.03286278560235</v>
       </c>
       <c r="CF41" s="417" t="n">
         <v>18.58548072111209</v>
@@ -10317,28 +10317,28 @@
         <v>20.24652483881341</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>-1.634343993504075</v>
+        <v>-1.634343993504054</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>-2.038682995275153</v>
+        <v>-2.038682995275138</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>-0.2537344082495459</v>
+        <v>-0.2537344082495387</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>-0.3050486998708379</v>
+        <v>-0.3050486998708344</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>-0.3512882804512678</v>
+        <v>-0.3512882804512607</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0.007181985488295977</v>
       </c>
       <c r="DD41" s="423" t="n">
-        <v>0.007725710458503227</v>
+        <v>0.007725710458503228</v>
       </c>
       <c r="DE41" s="423" t="n">
-        <v>0.02273859346923521</v>
+        <v>0.0227385934692352</v>
       </c>
       <c r="DF41" s="423" t="n">
         <v>0.02153261568521101</v>
@@ -10554,25 +10554,25 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>558365.1154446254</v>
+        <v>558365.1154446253</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>722963.0125383056</v>
+        <v>722963.0125383055</v>
       </c>
       <c r="BU42" s="440" t="n">
         <v>335712.0464231662</v>
       </c>
       <c r="BV42" s="440" t="n">
-        <v>296060.3965383624</v>
+        <v>296060.3965383623</v>
       </c>
       <c r="BW42" s="441" t="n">
         <v>358082.3922811655</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>6.552873190447237</v>
+        <v>6.552873190447235</v>
       </c>
       <c r="BY42" s="443" t="n">
-        <v>8.960062688986913</v>
+        <v>8.960062688986911</v>
       </c>
       <c r="BZ42" s="443" t="n">
         <v>4.211582972667646</v>
@@ -10581,22 +10581,22 @@
         <v>3.486320854276573</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>3.97802386096829</v>
+        <v>3.978023860968289</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.9617838403237748</v>
+        <v>0.9617838403237747</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>1.230139733020118</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>0.5642600933153782</v>
+        <v>0.5642600933153781</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.4915265485379859</v>
+        <v>0.4915265485379858</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>0.5850962548431877</v>
+        <v>0.5850962548431876</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11440,43 +11440,43 @@
         <v>13652829.57775516</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>15413843.69848081</v>
+        <v>15413843.6984808</v>
       </c>
       <c r="BV47" s="375" t="n">
-        <v>17852598.59062992</v>
+        <v>17852598.59062991</v>
       </c>
       <c r="BW47" s="392" t="n">
         <v>19810500.25376473</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>222.6082171202979</v>
+        <v>222.6082171202978</v>
       </c>
       <c r="BY47" s="372" t="n">
         <v>257.1762540061331</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>292.1642801895782</v>
+        <v>292.1642801895781</v>
       </c>
       <c r="CA47" s="372" t="n">
-        <v>320.7007119048811</v>
+        <v>320.700711904881</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>342.1348723613769</v>
+        <v>342.1348723613768</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>41.00609317615556</v>
+        <v>41.00609317615555</v>
       </c>
       <c r="CD47" s="389" t="n">
         <v>45.57324842173283</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>50.81005218525132</v>
+        <v>50.81005218525131</v>
       </c>
       <c r="CF47" s="389" t="n">
-        <v>58.09169742555951</v>
+        <v>58.09169742555949</v>
       </c>
       <c r="CG47" s="390" t="n">
-        <v>63.36045448144259</v>
+        <v>63.36045448144257</v>
       </c>
     </row>
     <row r="48">
@@ -11686,25 +11686,25 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>6791360.615623762</v>
+        <v>6791360.61562376</v>
       </c>
       <c r="BT48" s="375" t="n">
-        <v>6320138.304217424</v>
+        <v>6320138.304217423</v>
       </c>
       <c r="BU48" s="375" t="n">
         <v>6980539.802886716</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>8030003.027625098</v>
+        <v>8030003.027625097</v>
       </c>
       <c r="BW48" s="392" t="n">
         <v>8924374.538327036</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>304.4930117058337</v>
+        <v>304.4930117058336</v>
       </c>
       <c r="BY48" s="372" t="n">
-        <v>347.3800017063943</v>
+        <v>347.3800017063942</v>
       </c>
       <c r="BZ48" s="372" t="n">
         <v>425.7087797595168</v>
@@ -11716,16 +11716,16 @@
         <v>482.532320738689</v>
       </c>
       <c r="CC48" s="386" t="n">
-        <v>25.03083343969871</v>
+        <v>25.0308334396987</v>
       </c>
       <c r="CD48" s="372" t="n">
-        <v>23.10818145901084</v>
+        <v>23.10818145901083</v>
       </c>
       <c r="CE48" s="372" t="n">
         <v>25.32668220472561</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>28.93376264150738</v>
+        <v>28.93376264150737</v>
       </c>
       <c r="CG48" s="387" t="n">
         <v>31.86146664327442</v>
@@ -12190,13 +12190,13 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>7879505.517718391</v>
+        <v>7879505.51771839</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>9264333.420513242</v>
+        <v>9264333.420513241</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>9210107.874456571</v>
+        <v>9210107.87445657</v>
       </c>
       <c r="BV50" s="420" t="n">
         <v>10915749.91958313</v>
@@ -12205,34 +12205,34 @@
         <v>13012027.24759934</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>977.4180842620627</v>
+        <v>977.4180842620624</v>
       </c>
       <c r="BY50" s="417" t="n">
         <v>1019.233029543745</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>898.5105926452326</v>
+        <v>898.5105926452325</v>
       </c>
       <c r="CA50" s="417" t="n">
         <v>939.7454315634828</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>982.1007605353429</v>
+        <v>982.1007605353426</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>855.1977867881255</v>
+        <v>855.1977867881252</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>897.2649103772727</v>
+        <v>897.2649103772725</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>791.665109557127</v>
+        <v>791.6651095571269</v>
       </c>
       <c r="CF50" s="417" t="n">
         <v>833.6254045646929</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>879.0548102506638</v>
+        <v>879.0548102506635</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12442,49 +12442,49 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>26993822.54076284</v>
+        <v>26993822.54076283</v>
       </c>
       <c r="BT51" s="440" t="n">
         <v>29436256.96301101</v>
       </c>
       <c r="BU51" s="440" t="n">
-        <v>31827814.0019553</v>
+        <v>31827814.00195529</v>
       </c>
       <c r="BV51" s="440" t="n">
-        <v>37066236.45054751</v>
+        <v>37066236.4505475</v>
       </c>
       <c r="BW51" s="441" t="n">
-        <v>42064073.68769295</v>
+        <v>42064073.68769294</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>316.7946763547364</v>
+        <v>316.7946763547362</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>364.8190891421732</v>
+        <v>364.8190891421731</v>
       </c>
       <c r="BZ51" s="417" t="n">
         <v>399.2870703808555</v>
       </c>
       <c r="CA51" s="417" t="n">
-        <v>436.4811863999034</v>
+        <v>436.4811863999033</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>467.2999634335059</v>
+        <v>467.2999634335058</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>46.49685589258146</v>
+        <v>46.49685589258145</v>
       </c>
       <c r="CD51" s="417" t="n">
-        <v>50.08653092010205</v>
+        <v>50.08653092010204</v>
       </c>
       <c r="CE51" s="417" t="n">
-        <v>53.49574282517764</v>
+        <v>53.49574282517762</v>
       </c>
       <c r="CF51" s="417" t="n">
-        <v>61.53825193390818</v>
+        <v>61.53825193390817</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>68.73147775105373</v>
+        <v>68.73147775105372</v>
       </c>
     </row>
     <row r="52">
@@ -13656,31 +13656,31 @@
         <v>153.9376778700135</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>105.4421873202927</v>
+        <v>105.4421873202926</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>115.223084316392</v>
+        <v>115.2230843163921</v>
       </c>
       <c r="DC58" s="393" t="n">
         <v>0.002312970317654127</v>
       </c>
       <c r="DD58" s="394" t="n">
-        <v>0.001301147648035755</v>
+        <v>0.001301147648035756</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.001357727510646706</v>
+        <v>0.001357727510646705</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.001439032452503423</v>
       </c>
       <c r="DG58" s="395" t="n">
-        <v>0.001537291150273705</v>
+        <v>0.001537291150273706</v>
       </c>
     </row>
     <row r="59">
@@ -13980,13 +13980,13 @@
         <v>0.002446357485112198</v>
       </c>
       <c r="DD59" s="397" t="n">
-        <v>0.0008102015015598327</v>
+        <v>0.0008102015015598329</v>
       </c>
       <c r="DE59" s="397" t="n">
-        <v>0.0008235172851865144</v>
+        <v>0.0008235172851865146</v>
       </c>
       <c r="DF59" s="397" t="n">
-        <v>0.0008877551560264621</v>
+        <v>0.0008877551560264623</v>
       </c>
       <c r="DG59" s="398" t="n">
         <v>0.0009421819582287481</v>
@@ -14523,7 +14523,7 @@
         <v>1553.115988492877</v>
       </c>
       <c r="BX61" s="211" t="n">
-        <v>8061.550778106699</v>
+        <v>8061.5507781067</v>
       </c>
       <c r="BY61" s="212" t="n">
         <v>9089.514519226654</v>
@@ -14538,7 +14538,7 @@
         <v>13249.17744744082</v>
       </c>
       <c r="CC61" s="212" t="n">
-        <v>9213.664534038991</v>
+        <v>9213.664534038993</v>
       </c>
       <c r="CD61" s="212" t="n">
         <v>10325.08160451507</v>
@@ -14580,19 +14580,19 @@
         <v>347856</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>505.05037259334</v>
+        <v>505.0503725933393</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>577.7063301463014</v>
+        <v>577.7063301463007</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0.04149604074682884</v>
@@ -14604,10 +14604,10 @@
         <v>0.03962628008369905</v>
       </c>
       <c r="DF61" s="423" t="n">
-        <v>0.03980905414698188</v>
+        <v>0.03980905414698189</v>
       </c>
       <c r="DG61" s="424" t="n">
-        <v>0.03989846882937716</v>
+        <v>0.03989846882937718</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" thickBot="1">
@@ -14889,19 +14889,19 @@
         <v>30690380.72727273</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>633.492864235678</v>
+        <v>633.4928642356773</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>718.2499130083107</v>
+        <v>718.24991300831</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -16564,28 +16564,28 @@
         <v>0.6264867851815534</v>
       </c>
       <c r="BZ70" s="467" t="n">
-        <v>0.6215135643752643</v>
+        <v>0.6215135643752644</v>
       </c>
       <c r="CA70" s="467" t="n">
-        <v>0.6321062005032161</v>
+        <v>0.6321062005032162</v>
       </c>
       <c r="CB70" s="468" t="n">
-        <v>0.6406163675199577</v>
+        <v>0.6406163675199578</v>
       </c>
       <c r="CC70" s="212" t="n">
-        <v>5012.113250236527</v>
+        <v>5012.113250236528</v>
       </c>
       <c r="CD70" s="212" t="n">
         <v>5694.460730011359</v>
       </c>
       <c r="CE70" s="212" t="n">
-        <v>6370.772943791366</v>
+        <v>6370.772943791368</v>
       </c>
       <c r="CF70" s="212" t="n">
-        <v>7342.321628349273</v>
+        <v>7342.321628349274</v>
       </c>
       <c r="CG70" s="213" t="n">
-        <v>8487.639929006884</v>
+        <v>8487.639929006886</v>
       </c>
       <c r="CW70" s="465" t="n"/>
       <c r="CX70" s="465" t="n"/>
@@ -18514,7 +18514,7 @@
         <v>0.1129242275987817</v>
       </c>
       <c r="CB79" s="468" t="n">
-        <v>0.1049240102700957</v>
+        <v>0.1049240102700956</v>
       </c>
       <c r="CC79" s="492" t="n">
         <v>0</v>
@@ -20887,34 +20887,34 @@
         </is>
       </c>
       <c r="C96" s="369" t="n">
-        <v>32787592.562044</v>
+        <v>32767786.992122</v>
       </c>
       <c r="D96" s="368" t="n">
-        <v>34909841.329031</v>
+        <v>34886969.337678</v>
       </c>
       <c r="E96" s="368" t="n">
-        <v>37725347.063863</v>
+        <v>37697900.67424</v>
       </c>
       <c r="F96" s="368" t="n">
-        <v>41998547.116991</v>
+        <v>41965611.449442</v>
       </c>
       <c r="G96" s="370" t="n">
-        <v>45874589.449385</v>
+        <v>45835066.648327</v>
       </c>
       <c r="H96" s="371" t="n">
-        <v>656.2462028179551</v>
+        <v>655.8497928030581</v>
       </c>
       <c r="I96" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339025</v>
       </c>
       <c r="J96" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="K96" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903365</v>
       </c>
       <c r="L96" s="373" t="n">
-        <v>875.6820672931149</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="S96" s="72" t="inlineStr">
         <is>
@@ -20922,34 +20922,34 @@
         </is>
       </c>
       <c r="T96" s="374" t="n">
-        <v>35768282.79495709</v>
+        <v>35746676.71867854</v>
       </c>
       <c r="U96" s="375" t="n">
-        <v>38083463.26803382</v>
+        <v>38058512.00473963</v>
       </c>
       <c r="V96" s="375" t="n">
-        <v>41154924.06966873</v>
+        <v>41124982.55371637</v>
       </c>
       <c r="W96" s="375" t="n">
-        <v>45816596.85489927</v>
+        <v>45780667.03575491</v>
       </c>
       <c r="X96" s="376" t="n">
-        <v>50045006.67205637</v>
+        <v>50001890.889084</v>
       </c>
       <c r="Y96" s="377" t="n">
-        <v>656.2462028179552</v>
+        <v>655.849792803058</v>
       </c>
       <c r="Z96" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339024</v>
       </c>
       <c r="AA96" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="AB96" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903366</v>
       </c>
       <c r="AC96" s="378" t="n">
-        <v>875.6820672931148</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="AJ96" s="78" t="inlineStr">
         <is>
@@ -20957,34 +20957,34 @@
         </is>
       </c>
       <c r="AK96" s="506" t="n">
-        <v>35125477.462638</v>
+        <v>35123316.85501</v>
       </c>
       <c r="AL96" s="368" t="n">
-        <v>37283748.150441</v>
+        <v>37281253.024112</v>
       </c>
       <c r="AM96" s="368" t="n">
-        <v>40190353.399759</v>
+        <v>40187359.248164</v>
       </c>
       <c r="AN96" s="368" t="n">
-        <v>44653512.492535</v>
+        <v>44649919.51062</v>
       </c>
       <c r="AO96" s="380" t="n">
-        <v>48642442.929692</v>
+        <v>48638131.351394</v>
       </c>
       <c r="AP96" s="381" t="n">
-        <v>650.0909759839683</v>
+        <v>650.0509881568107</v>
       </c>
       <c r="AQ96" s="372" t="n">
-        <v>713.2740639286853</v>
+        <v>713.2263297553528</v>
       </c>
       <c r="AR96" s="372" t="n">
-        <v>778.4654918735082</v>
+        <v>778.4074967702812</v>
       </c>
       <c r="AS96" s="372" t="n">
-        <v>823.50842076685</v>
+        <v>823.4421583230353</v>
       </c>
       <c r="AT96" s="382" t="n">
-        <v>866.6242250553507</v>
+        <v>866.5474090490767</v>
       </c>
       <c r="AU96" s="379" t="n">
         <v>27662091.03085308</v>
@@ -21007,34 +21007,34 @@
         </is>
       </c>
       <c r="BB96" s="391" t="n">
-        <v>35125477.462638</v>
+        <v>35123316.85501</v>
       </c>
       <c r="BC96" s="375" t="n">
-        <v>37283748.150441</v>
+        <v>37281253.024112</v>
       </c>
       <c r="BD96" s="375" t="n">
-        <v>40190353.399759</v>
+        <v>40187359.248164</v>
       </c>
       <c r="BE96" s="375" t="n">
-        <v>44653512.492535</v>
+        <v>44649919.51062</v>
       </c>
       <c r="BF96" s="392" t="n">
-        <v>48642442.929692</v>
+        <v>48638131.351394</v>
       </c>
       <c r="BG96" s="386" t="n">
-        <v>650.0909759839683</v>
+        <v>650.0509881568107</v>
       </c>
       <c r="BH96" s="372" t="n">
-        <v>713.2740639286853</v>
+        <v>713.2263297553528</v>
       </c>
       <c r="BI96" s="372" t="n">
-        <v>778.4654918735082</v>
+        <v>778.4074967702812</v>
       </c>
       <c r="BJ96" s="372" t="n">
-        <v>823.50842076685</v>
+        <v>823.4421583230353</v>
       </c>
       <c r="BK96" s="387" t="n">
-        <v>866.6242250553507</v>
+        <v>866.5474090490767</v>
       </c>
       <c r="BR96" s="83" t="inlineStr">
         <is>
@@ -21042,34 +21042,34 @@
         </is>
       </c>
       <c r="BS96" s="391" t="n">
-        <v>35417841.95783767</v>
+        <v>35415663.36654072</v>
       </c>
       <c r="BT96" s="375" t="n">
-        <v>37865895.80241317</v>
+        <v>37863361.71723466</v>
       </c>
       <c r="BU96" s="375" t="n">
-        <v>41069857.71365783</v>
+        <v>41066798.03964211</v>
       </c>
       <c r="BV96" s="375" t="n">
-        <v>45842633.72734463</v>
+        <v>45838945.0644663</v>
       </c>
       <c r="BW96" s="392" t="n">
-        <v>50179799.88968757</v>
+        <v>50175352.04284494</v>
       </c>
       <c r="BX96" s="386" t="n">
-        <v>650.0909759839683</v>
+        <v>650.0509881568107</v>
       </c>
       <c r="BY96" s="372" t="n">
-        <v>713.2740639286853</v>
+        <v>713.2263297553528</v>
       </c>
       <c r="BZ96" s="372" t="n">
-        <v>778.4654918735082</v>
+        <v>778.4074967702812</v>
       </c>
       <c r="CA96" s="372" t="n">
-        <v>823.50842076685</v>
+        <v>823.4421583230353</v>
       </c>
       <c r="CB96" s="387" t="n">
-        <v>866.6242250553507</v>
+        <v>866.5474090490767</v>
       </c>
       <c r="CW96" s="511" t="n">
         <v>0</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>23309474.0036263</v>
+        <v>23309474.00362628</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>24522422.72329189</v>
+        <v>24522422.72329186</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>26271822.68134406</v>
+        <v>26271822.68134405</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>29440637.38162521</v>
+        <v>29440637.38162518</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>32281148.46266282</v>
+        <v>32281148.46266283</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21320,10 +21320,10 @@
         <v>12593348.66790533</v>
       </c>
       <c r="DE97" s="375" t="n">
-        <v>11736504.40934544</v>
+        <v>11736504.40934543</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>12982474.12633856</v>
+        <v>12982474.12633855</v>
       </c>
       <c r="DG97" s="392" t="n">
         <v>14323143.8639617</v>
@@ -21544,13 +21544,13 @@
         <v>386133.3526453226</v>
       </c>
       <c r="DD98" s="375" t="n">
-        <v>355474.5971755303</v>
+        <v>355474.5971755304</v>
       </c>
       <c r="DE98" s="375" t="n">
         <v>363637.4607713409</v>
       </c>
       <c r="DF98" s="375" t="n">
-        <v>424288.0975007447</v>
+        <v>424288.0975007446</v>
       </c>
       <c r="DG98" s="392" t="n">
         <v>491540.9522200545</v>
@@ -21735,7 +21735,7 @@
         <v>72852319.767851</v>
       </c>
       <c r="BW99" s="421" t="n">
-        <v>81467333.23752056</v>
+        <v>81467333.23752058</v>
       </c>
       <c r="BX99" s="416" t="n">
         <v>6805.890279756461</v>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>23375332.55454774</v>
+        <v>23375332.55454772</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>25865808.62000421</v>
+        <v>25865808.62000422</v>
       </c>
       <c r="DE99" s="420" t="n">
-        <v>24844698.31488091</v>
+        <v>24844698.3148809</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>28670741.24720033</v>
+        <v>28670741.24720032</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>33264716.1504626</v>
+        <v>33264716.15046259</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21795,34 +21795,34 @@
         </is>
       </c>
       <c r="C100" s="425" t="n">
-        <v>105887411.079127</v>
+        <v>105867605.509205</v>
       </c>
       <c r="D100" s="425" t="n">
-        <v>111318078.993001</v>
+        <v>111295207.001648</v>
       </c>
       <c r="E100" s="425" t="n">
-        <v>118734694.789955</v>
+        <v>118707248.400332</v>
       </c>
       <c r="F100" s="425" t="n">
-        <v>131767816.011281</v>
+        <v>131734880.343732</v>
       </c>
       <c r="G100" s="426" t="n">
-        <v>145759194.782227</v>
+        <v>145719671.981169</v>
       </c>
       <c r="H100" s="427" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118435</v>
       </c>
       <c r="I100" s="427" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="J100" s="427" t="n">
-        <v>1648.243903578627</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="K100" s="427" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="L100" s="428" t="n">
-        <v>1805.533728250066</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="S100" s="143" t="inlineStr">
         <is>
@@ -21830,34 +21830,34 @@
         </is>
       </c>
       <c r="T100" s="429" t="n">
-        <v>115513539.3590477</v>
+        <v>115491933.2827691</v>
       </c>
       <c r="U100" s="430" t="n">
-        <v>121437904.3560011</v>
+        <v>121412953.0927069</v>
       </c>
       <c r="V100" s="430" t="n">
-        <v>129528757.9526782</v>
+        <v>129498816.4367258</v>
       </c>
       <c r="W100" s="430" t="n">
-        <v>143746708.3759429</v>
+        <v>143710778.5567985</v>
       </c>
       <c r="X100" s="431" t="n">
-        <v>159010030.6715204</v>
+        <v>158966914.888548</v>
       </c>
       <c r="Y100" s="432" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118434</v>
       </c>
       <c r="Z100" s="433" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="AA100" s="433" t="n">
-        <v>1648.243903578626</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="AB100" s="433" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="AC100" s="434" t="n">
-        <v>1805.533728250067</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="AJ100" s="150" t="inlineStr">
         <is>
@@ -21865,34 +21865,34 @@
         </is>
       </c>
       <c r="AK100" s="435" t="n">
-        <v>114843279.30167</v>
+        <v>114841118.694042</v>
       </c>
       <c r="AL100" s="408" t="n">
-        <v>120604309.155498</v>
+        <v>120601814.029169</v>
       </c>
       <c r="AM100" s="408" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.031681</v>
       </c>
       <c r="AN100" s="408" t="n">
-        <v>142534836.694189</v>
+        <v>142531243.712274</v>
       </c>
       <c r="AO100" s="409" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.56759</v>
       </c>
       <c r="AP100" s="436" t="n">
-        <v>1357.224067168913</v>
+        <v>1357.198532991465</v>
       </c>
       <c r="AQ100" s="437" t="n">
-        <v>1518.294782277387</v>
+        <v>1518.263370984433</v>
       </c>
       <c r="AR100" s="437" t="n">
-        <v>1650.557554124222</v>
+        <v>1650.519101869699</v>
       </c>
       <c r="AS100" s="437" t="n">
-        <v>1727.377841274013</v>
+        <v>1727.334297972684</v>
       </c>
       <c r="AT100" s="438" t="n">
-        <v>1810.230081002933</v>
+        <v>1810.180541160799</v>
       </c>
       <c r="AU100" s="435" t="n">
         <v>76469169.51897734</v>
@@ -21915,34 +21915,34 @@
         </is>
       </c>
       <c r="BB100" s="439" t="n">
-        <v>114843279.30167</v>
+        <v>114841118.694042</v>
       </c>
       <c r="BC100" s="440" t="n">
-        <v>120604309.155498</v>
+        <v>120601814.029169</v>
       </c>
       <c r="BD100" s="440" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.031681</v>
       </c>
       <c r="BE100" s="440" t="n">
-        <v>142534836.694189</v>
+        <v>142531243.712274</v>
       </c>
       <c r="BF100" s="441" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.56759</v>
       </c>
       <c r="BG100" s="442" t="n">
-        <v>1357.224067168913</v>
+        <v>1357.198532991465</v>
       </c>
       <c r="BH100" s="443" t="n">
-        <v>1518.294782277387</v>
+        <v>1518.263370984433</v>
       </c>
       <c r="BI100" s="443" t="n">
-        <v>1650.557554124222</v>
+        <v>1650.519101869699</v>
       </c>
       <c r="BJ100" s="443" t="n">
-        <v>1727.377841274013</v>
+        <v>1727.334297972684</v>
       </c>
       <c r="BK100" s="444" t="n">
-        <v>1810.230081002933</v>
+        <v>1810.180541160799</v>
       </c>
       <c r="BR100" s="155" t="inlineStr">
         <is>
@@ -21950,34 +21950,34 @@
         </is>
       </c>
       <c r="BS100" s="439" t="n">
-        <v>113279322.2546358</v>
+        <v>113277143.6633389</v>
       </c>
       <c r="BT100" s="440" t="n">
-        <v>119575552.2050129</v>
+        <v>119573018.1198344</v>
       </c>
       <c r="BU100" s="440" t="n">
-        <v>128311818.005852</v>
+        <v>128308758.3318363</v>
       </c>
       <c r="BV100" s="440" t="n">
-        <v>142902075.4076022</v>
+        <v>142898386.7447238</v>
       </c>
       <c r="BW100" s="441" t="n">
-        <v>158512834.2170617</v>
+        <v>158508386.3702191</v>
       </c>
       <c r="BX100" s="442" t="n">
-        <v>1329.4258779819</v>
+        <v>1329.400310423849</v>
       </c>
       <c r="BY100" s="443" t="n">
-        <v>1481.963012278412</v>
+        <v>1481.931606021571</v>
       </c>
       <c r="BZ100" s="443" t="n">
-        <v>1609.700556364026</v>
+        <v>1609.662172066757</v>
       </c>
       <c r="CA100" s="443" t="n">
-        <v>1682.773148445647</v>
+        <v>1682.729711827756</v>
       </c>
       <c r="CB100" s="444" t="n">
-        <v>1760.957395218868</v>
+        <v>1760.907983013043</v>
       </c>
       <c r="CC100" s="368" t="n"/>
       <c r="CD100" s="368" t="n"/>
@@ -21997,19 +21997,19 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>62453967.34084317</v>
+        <v>62453967.34084314</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>63337054.60837696</v>
+        <v>63337054.60837694</v>
       </c>
       <c r="DE100" s="440" t="n">
-        <v>63216662.86634175</v>
+        <v>63216662.86634173</v>
       </c>
       <c r="DF100" s="440" t="n">
-        <v>71518140.85266484</v>
+        <v>71518140.85266478</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>80360549.42930716</v>
+        <v>80360549.42930718</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23084,31 +23084,31 @@
         <v>153.9376778700135</v>
       </c>
       <c r="BY108" s="190" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="BZ108" s="190" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="CA108" s="190" t="n">
-        <v>105.4421873202927</v>
+        <v>105.4421873202926</v>
       </c>
       <c r="CB108" s="198" t="n">
-        <v>115.223084316392</v>
+        <v>115.2230843163921</v>
       </c>
       <c r="CC108" s="199" t="n">
         <v>153.9376778700135</v>
       </c>
       <c r="CD108" s="200" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="CE108" s="200" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="CF108" s="200" t="n">
-        <v>105.4421873202927</v>
+        <v>105.4421873202926</v>
       </c>
       <c r="CG108" s="201" t="n">
-        <v>115.223084316392</v>
+        <v>115.2230843163921</v>
       </c>
       <c r="CI108" s="199" t="n">
         <v>0</v>
@@ -23141,16 +23141,16 @@
         <v>153.9376778700135</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>105.4421873202927</v>
+        <v>105.4421873202926</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>115.223084316392</v>
+        <v>115.2230843163921</v>
       </c>
     </row>
     <row r="109">
@@ -23966,34 +23966,34 @@
         <v>0</v>
       </c>
       <c r="BX111" s="211" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="BY111" s="212" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="BZ111" s="212" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="CA111" s="212" t="n">
-        <v>505.05037259334</v>
+        <v>505.0503725933393</v>
       </c>
       <c r="CB111" s="213" t="n">
-        <v>577.7063301463014</v>
+        <v>577.7063301463007</v>
       </c>
       <c r="CC111" s="212" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="CD111" s="212" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="CE111" s="212" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="CF111" s="212" t="n">
-        <v>505.05037259334</v>
+        <v>505.0503725933393</v>
       </c>
       <c r="CG111" s="213" t="n">
-        <v>577.7063301463014</v>
+        <v>577.7063301463007</v>
       </c>
       <c r="CI111" s="211" t="n">
         <v>0</v>
@@ -24023,19 +24023,19 @@
         <v>0</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>505.05037259334</v>
+        <v>505.0503725933393</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>577.7063301463014</v>
+        <v>577.7063301463007</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24261,34 +24261,34 @@
         <v>0</v>
       </c>
       <c r="BX112" s="221" t="n">
-        <v>592.6294401595057</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="BY112" s="222" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="BZ112" s="222" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="CA112" s="222" t="n">
-        <v>633.4928642356781</v>
+        <v>633.4928642356773</v>
       </c>
       <c r="CB112" s="214" t="n">
-        <v>718.2499130083107</v>
+        <v>718.24991300831</v>
       </c>
       <c r="CC112" s="222" t="n">
-        <v>592.6294401595057</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="CD112" s="222" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="CE112" s="222" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="CF112" s="222" t="n">
-        <v>633.4928642356781</v>
+        <v>633.4928642356773</v>
       </c>
       <c r="CG112" s="214" t="n">
-        <v>718.2499130083107</v>
+        <v>718.24991300831</v>
       </c>
       <c r="CI112" s="349" t="n">
         <v>0</v>
@@ -24318,19 +24318,19 @@
         <v>0</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>633.492864235678</v>
+        <v>633.4928642356773</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>718.2499130083107</v>
+        <v>718.24991300831</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -30296,49 +30296,49 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>100073.4952472228</v>
+        <v>100067.3396139671</v>
       </c>
       <c r="BT146" s="375" t="n">
-        <v>67653.05219158107</v>
+        <v>67648.52467167942</v>
       </c>
       <c r="BU146" s="375" t="n">
-        <v>74872.12527677791</v>
+        <v>74866.547358836</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>86832.52916233659</v>
+        <v>86825.54230532356</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>99855.11615418058</v>
+        <v>99846.26517701286</v>
       </c>
       <c r="BX146" s="386" t="n">
-        <v>650.0909759839683</v>
+        <v>650.0509881568107</v>
       </c>
       <c r="BY146" s="372" t="n">
-        <v>713.2740639286855</v>
+        <v>713.2263297553529</v>
       </c>
       <c r="BZ146" s="372" t="n">
-        <v>778.4654918735081</v>
+        <v>778.4074967702812</v>
       </c>
       <c r="CA146" s="372" t="n">
-        <v>823.5084207668501</v>
+        <v>823.4421583230353</v>
       </c>
       <c r="CB146" s="387" t="n">
-        <v>866.6242250553507</v>
+        <v>866.5474090490767</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>100073.4952472228</v>
+        <v>100067.3396139671</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>67653.05219158107</v>
+        <v>67648.52467167942</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>74872.12527677791</v>
+        <v>74866.547358836</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>86832.52916233659</v>
+        <v>86825.54230532356</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>99855.11615418058</v>
+        <v>99846.26517701286</v>
       </c>
     </row>
     <row r="147">
@@ -30872,28 +30872,28 @@
         </is>
       </c>
       <c r="BS149" s="419" t="n">
-        <v>2484940.964265611</v>
+        <v>2484940.964265607</v>
       </c>
       <c r="BT149" s="420" t="n">
-        <v>2758991.772798026</v>
+        <v>2758991.772798021</v>
       </c>
       <c r="BU149" s="420" t="n">
-        <v>2838037.726098412</v>
+        <v>2838037.726098408</v>
       </c>
       <c r="BV149" s="420" t="n">
-        <v>3167632.037094106</v>
+        <v>3167632.037094102</v>
       </c>
       <c r="BW149" s="421" t="n">
-        <v>3552235.170685605</v>
+        <v>3552235.1706856</v>
       </c>
       <c r="BX149" s="416" t="n">
         <v>6805.890279756461</v>
       </c>
       <c r="BY149" s="417" t="n">
-        <v>6671.509778471568</v>
+        <v>6671.509778471569</v>
       </c>
       <c r="BZ149" s="417" t="n">
-        <v>6401.744478310518</v>
+        <v>6401.744478310519</v>
       </c>
       <c r="CA149" s="417" t="n">
         <v>6271.913078350785</v>
@@ -30902,19 +30902,19 @@
         <v>6148.859697947256</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>2484940.964265611</v>
+        <v>2484940.964265607</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>2758991.772798026</v>
+        <v>2758991.772798021</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>2838037.726098412</v>
+        <v>2838037.726098408</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>3167632.037094106</v>
+        <v>3167632.037094102</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>3552235.170685605</v>
+        <v>3552235.1706856</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -31064,49 +31064,49 @@
         </is>
       </c>
       <c r="BS150" s="439" t="n">
-        <v>2659719.932381264</v>
+        <v>2659713.776748005</v>
       </c>
       <c r="BT150" s="440" t="n">
-        <v>2856950.186199287</v>
+        <v>2856945.658679382</v>
       </c>
       <c r="BU150" s="440" t="n">
-        <v>2940811.00980268</v>
+        <v>2940805.431884734</v>
       </c>
       <c r="BV150" s="440" t="n">
-        <v>3286062.420887841</v>
+        <v>3286055.434030824</v>
       </c>
       <c r="BW150" s="441" t="n">
-        <v>3688172.60269317</v>
+        <v>3688163.751715998</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>4487.99832094977</v>
+        <v>4487.987933964517</v>
       </c>
       <c r="BY150" s="443" t="n">
-        <v>5339.685539158851</v>
+        <v>5339.677077151825</v>
       </c>
       <c r="BZ150" s="443" t="n">
-        <v>5241.767853612731</v>
+        <v>5241.757911406018</v>
       </c>
       <c r="CA150" s="443" t="n">
-        <v>5187.213000185159</v>
+        <v>5187.201971083794</v>
       </c>
       <c r="CB150" s="444" t="n">
-        <v>5134.943333645061</v>
+        <v>5134.931010668047</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>2659719.932381265</v>
+        <v>2659713.776748005</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>2856950.186199287</v>
+        <v>2856945.658679381</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>2940811.00980268</v>
+        <v>2940805.431884734</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>3286062.420887841</v>
+        <v>3286055.434030824</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>3688172.60269317</v>
+        <v>3688163.751715998</v>
       </c>
     </row>
     <row r="151">
@@ -34186,7 +34186,7 @@
         <v>253199.495729278</v>
       </c>
       <c r="AO172" s="195" t="n">
-        <v>256650.059681456</v>
+        <v>256650.059681455</v>
       </c>
       <c r="AP172" s="194" t="n">
         <v>54031.633663863</v>
@@ -34210,13 +34210,13 @@
         <v>299674.7567900986</v>
       </c>
       <c r="AW172" s="190" t="n">
-        <v>303458.2705868938</v>
+        <v>303458.2705868937</v>
       </c>
       <c r="AX172" s="190" t="n">
-        <v>307423.0001484926</v>
+        <v>307423.0001484928</v>
       </c>
       <c r="AY172" s="196" t="n">
-        <v>312778.7040500476</v>
+        <v>312778.7040500475</v>
       </c>
       <c r="BA172" s="83" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>253199.495729278</v>
       </c>
       <c r="BF172" s="198" t="n">
-        <v>256650.059681456</v>
+        <v>256650.059681455</v>
       </c>
       <c r="BG172" s="197" t="n">
         <v>54031.633663863</v>
@@ -34266,7 +34266,7 @@
         <v>307423.000148493</v>
       </c>
       <c r="BP172" s="201" t="n">
-        <v>312778.704050048</v>
+        <v>312778.704050047</v>
       </c>
       <c r="BR172" s="83" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>251650.08380853</v>
       </c>
       <c r="BW172" s="198" t="n">
-        <v>254760.876308994</v>
+        <v>254760.876308993</v>
       </c>
       <c r="BX172" s="197" t="n">
         <v>54481.36224955361</v>
@@ -34298,7 +34298,7 @@
         <v>52757.45443151312</v>
       </c>
       <c r="CA172" s="190" t="n">
-        <v>55667.47415264311</v>
+        <v>55667.47415264312</v>
       </c>
       <c r="CB172" s="198" t="n">
         <v>57902.60465673787</v>
@@ -34316,7 +34316,7 @@
         <v>307317.5579611731</v>
       </c>
       <c r="CG172" s="201" t="n">
-        <v>312663.4809657319</v>
+        <v>312663.4809657309</v>
       </c>
       <c r="CI172" s="199" t="n">
         <v>235452</v>
@@ -34483,19 +34483,19 @@
         <v>16827.718432066</v>
       </c>
       <c r="AU173" s="190" t="n">
-        <v>271392.0777568708</v>
+        <v>271392.0777568707</v>
       </c>
       <c r="AV173" s="190" t="n">
-        <v>273528.420438977</v>
+        <v>273528.4204389771</v>
       </c>
       <c r="AW173" s="190" t="n">
         <v>275641.0716215413</v>
       </c>
       <c r="AX173" s="190" t="n">
-        <v>277553.0635181831</v>
+        <v>277553.0635181832</v>
       </c>
       <c r="AY173" s="196" t="n">
-        <v>280124.0949150363</v>
+        <v>280124.0949150365</v>
       </c>
       <c r="BA173" s="101" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>1553.115988498</v>
       </c>
       <c r="BX175" s="211" t="n">
-        <v>8061.550778031534</v>
+        <v>8061.550778031535</v>
       </c>
       <c r="BY175" s="212" t="n">
         <v>9089.514519189534</v>
@@ -35141,7 +35141,7 @@
         <v>13249.17744741269</v>
       </c>
       <c r="CC175" s="212" t="n">
-        <v>9213.664533961533</v>
+        <v>9213.664533961535</v>
       </c>
       <c r="CD175" s="212" t="n">
         <v>10325.08160448153</v>
@@ -35302,10 +35302,10 @@
         <v>520446.739646707</v>
       </c>
       <c r="AO176" s="208" t="n">
-        <v>525691.6649138341</v>
+        <v>525691.664913833</v>
       </c>
       <c r="AP176" s="206" t="n">
-        <v>84616.30034344201</v>
+        <v>84616.300343442</v>
       </c>
       <c r="AQ176" s="207" t="n">
         <v>79434.053625471</v>
@@ -35317,10 +35317,10 @@
         <v>82515.14711356201</v>
       </c>
       <c r="AT176" s="208" t="n">
-        <v>87032.54011691701</v>
+        <v>87032.54011691699</v>
       </c>
       <c r="AU176" s="207" t="n">
-        <v>581144.1962621955</v>
+        <v>581144.1962621954</v>
       </c>
       <c r="AV176" s="207" t="n">
         <v>588243.0818146194</v>
@@ -35329,10 +35329,10 @@
         <v>595520.7883944142</v>
       </c>
       <c r="AX176" s="207" t="n">
-        <v>602961.8867602693</v>
+        <v>602961.8867602695</v>
       </c>
       <c r="AY176" s="208" t="n">
-        <v>612724.2050307511</v>
+        <v>612724.2050307509</v>
       </c>
       <c r="BA176" s="155" t="inlineStr">
         <is>
@@ -35352,10 +35352,10 @@
         <v>520446.739646707</v>
       </c>
       <c r="BF176" s="214" t="n">
-        <v>525691.6649138341</v>
+        <v>525691.664913833</v>
       </c>
       <c r="BG176" s="221" t="n">
-        <v>84616.30034344201</v>
+        <v>84616.300343442</v>
       </c>
       <c r="BH176" s="222" t="n">
         <v>79434.053625471</v>
@@ -35367,7 +35367,7 @@
         <v>82515.14711356201</v>
       </c>
       <c r="BK176" s="214" t="n">
-        <v>87032.54011691701</v>
+        <v>87032.54011691699</v>
       </c>
       <c r="BL176" s="222" t="n">
         <v>581144.196262195</v>
@@ -35376,13 +35376,13 @@
         <v>588243.081814619</v>
       </c>
       <c r="BN176" s="222" t="n">
-        <v>595520.7883944151</v>
+        <v>595520.7883944149</v>
       </c>
       <c r="BO176" s="222" t="n">
-        <v>602961.8867602691</v>
+        <v>602961.8867602689</v>
       </c>
       <c r="BP176" s="214" t="n">
-        <v>612724.2050307509</v>
+        <v>612724.2050307499</v>
       </c>
       <c r="BR176" s="155" t="inlineStr">
         <is>
@@ -35402,13 +35402,13 @@
         <v>517407.811737436</v>
       </c>
       <c r="BW176" s="214" t="n">
-        <v>521990.810715448</v>
+        <v>521990.810715447</v>
       </c>
       <c r="BX176" s="221" t="n">
         <v>85209.20506365735</v>
       </c>
       <c r="BY176" s="222" t="n">
-        <v>80687.27168864202</v>
+        <v>80687.27168864201</v>
       </c>
       <c r="BZ176" s="222" t="n">
         <v>79711.60691899204</v>
@@ -35417,7 +35417,7 @@
         <v>84920.58215859803</v>
       </c>
       <c r="CB176" s="214" t="n">
-        <v>90015.14440229441</v>
+        <v>90015.14440229442</v>
       </c>
       <c r="CC176" s="222" t="n">
         <v>580551.5668220343</v>
@@ -35429,10 +35429,10 @@
         <v>594959.754199096</v>
       </c>
       <c r="CF176" s="222" t="n">
-        <v>602328.393896034</v>
+        <v>602328.3938960341</v>
       </c>
       <c r="CG176" s="214" t="n">
-        <v>612005.9551177424</v>
+        <v>612005.9551177415</v>
       </c>
       <c r="CI176" s="349" t="n">
         <v>485733.8181818182</v>
@@ -38458,22 +38458,22 @@
         <v>253199.495729278</v>
       </c>
       <c r="AO190" s="195" t="n">
-        <v>256650.059681456</v>
+        <v>256650.059681455</v>
       </c>
       <c r="AP190" s="194" t="n">
         <v>54031.63366386307</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>52271.27977257394</v>
+        <v>52271.27977257397</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>51627.66213746626</v>
+        <v>51627.66213746625</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>54223.50441921541</v>
+        <v>54223.50441921525</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>56128.64436859209</v>
+        <v>56128.6443685921</v>
       </c>
       <c r="AU190" s="190" t="n">
         <v>295914.8350787372</v>
@@ -38488,7 +38488,7 @@
         <v>307423.000148493</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>312778.7040500477</v>
+        <v>312778.7040500476</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38508,22 +38508,22 @@
         <v>253199.495729278</v>
       </c>
       <c r="BF190" s="198" t="n">
-        <v>256650.059681456</v>
+        <v>256650.059681455</v>
       </c>
       <c r="BG190" s="197" t="n">
         <v>54031.63366386307</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>52271.27977257394</v>
+        <v>52271.27977257397</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>51627.66213746626</v>
+        <v>51627.66213746625</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>54223.50441921541</v>
+        <v>54223.50441921525</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>56128.64436859209</v>
+        <v>56128.6443685921</v>
       </c>
       <c r="BL190" s="199" t="n">
         <v>295914.8350787371</v>
@@ -38535,10 +38535,10 @@
         <v>303458.2705868942</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>307423.0001484934</v>
+        <v>307423.0001484932</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>312778.7040500481</v>
+        <v>312778.7040500471</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38558,19 +38558,19 @@
         <v>251650.08380853</v>
       </c>
       <c r="BW190" s="198" t="n">
-        <v>254760.876308994</v>
+        <v>254760.876308993</v>
       </c>
       <c r="BX190" s="197" t="n">
         <v>54481.36224955368</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>53087.442425068</v>
+        <v>53087.44242506802</v>
       </c>
       <c r="BZ190" s="190" t="n">
         <v>52757.45443151338</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>55667.47415264353</v>
+        <v>55667.47415264337</v>
       </c>
       <c r="CB190" s="198" t="n">
         <v>57902.60465673797</v>
@@ -38582,13 +38582,13 @@
         <v>299579.908181951</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>303362.0914677704</v>
+        <v>303362.0914677703</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>307317.5579611735</v>
+        <v>307317.5579611734</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>312663.480965732</v>
+        <v>312663.480965731</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>235452</v>
@@ -38621,10 +38621,10 @@
         <v>153.9376778700171</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>94.8486081478395</v>
+        <v>94.84860814783953</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>96.17911912392225</v>
+        <v>96.17911912392221</v>
       </c>
       <c r="CZ190" s="92" t="n">
         <v>105.442187320283</v>
@@ -38642,10 +38642,10 @@
         <v>0.001357727510634444</v>
       </c>
       <c r="DF190" s="394" t="n">
-        <v>0.001439032452497706</v>
+        <v>0.00143903245249771</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.001537291150284877</v>
+        <v>0.001537291150284878</v>
       </c>
     </row>
     <row r="191">
@@ -38770,34 +38770,34 @@
         <v>263296.37648297</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>21822.47300476474</v>
+        <v>21822.47300476469</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>17388.43208225275</v>
+        <v>17388.43208225277</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>15304.94859204203</v>
+        <v>15304.94859204202</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>15927.9730211347</v>
+        <v>15927.97302113473</v>
       </c>
       <c r="AT191" s="195" t="n">
         <v>16827.71843206646</v>
       </c>
       <c r="AU191" s="190" t="n">
-        <v>271392.0777568705</v>
+        <v>271392.0777568704</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>273528.4204389767</v>
+        <v>273528.4204389768</v>
       </c>
       <c r="AW191" s="190" t="n">
         <v>275641.0716215413</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>277553.0635181828</v>
+        <v>277553.0635181829</v>
       </c>
       <c r="AY191" s="196" t="n">
-        <v>280124.0949150368</v>
+        <v>280124.0949150369</v>
       </c>
       <c r="BA191" s="101" t="inlineStr">
         <is>
@@ -38820,28 +38820,28 @@
         <v>263296.37648297</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>21822.47300476474</v>
+        <v>21822.47300476469</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>17388.43208225275</v>
+        <v>17388.43208225277</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>15304.94859204203</v>
+        <v>15304.94859204202</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>15927.9730211347</v>
+        <v>15927.97302113473</v>
       </c>
       <c r="BK191" s="198" t="n">
         <v>16827.71843206646</v>
       </c>
       <c r="BL191" s="197" t="n">
-        <v>271392.0777568708</v>
+        <v>271392.0777568707</v>
       </c>
       <c r="BM191" s="190" t="n">
-        <v>273528.4204389767</v>
+        <v>273528.4204389768</v>
       </c>
       <c r="BN191" s="190" t="n">
-        <v>275641.0716215411</v>
+        <v>275641.071621541</v>
       </c>
       <c r="BO191" s="190" t="n">
         <v>277553.0635181827</v>
@@ -38870,19 +38870,19 @@
         <v>261604.426949683</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>22303.83080881018</v>
+        <v>22303.83080881013</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>18193.73099562388</v>
+        <v>18193.7309956239</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>16397.45322341717</v>
+        <v>16397.45322341716</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>17304.32584270626</v>
+        <v>17304.32584270628</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>18494.87413547209</v>
+        <v>18494.87413547208</v>
       </c>
       <c r="CC191" s="197" t="n">
         <v>271319.7957222922</v>
@@ -38891,7 +38891,7 @@
         <v>273502.1929542139</v>
       </c>
       <c r="CE191" s="190" t="n">
-        <v>275619.9863235652</v>
+        <v>275619.9863235651</v>
       </c>
       <c r="CF191" s="190" t="n">
         <v>277530.5488996223</v>
@@ -38927,7 +38927,7 @@
         <v>23003650.90909091</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>72.28203457857771</v>
+        <v>72.28203457857769</v>
       </c>
       <c r="CX191" s="103" t="n">
         <v>26.22748476335996</v>
@@ -38939,22 +38939,22 @@
         <v>22.51461856008694</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>24.79382988119199</v>
+        <v>24.79382988119198</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.002446357485138571</v>
+        <v>0.002446357485138576</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.0008102015015480561</v>
+        <v>0.0008102015015480552</v>
       </c>
       <c r="DE191" s="397" t="n">
-        <v>0.0008235172851842531</v>
+        <v>0.0008235172851842537</v>
       </c>
       <c r="DF191" s="397" t="n">
-        <v>0.0008877551560189543</v>
+        <v>0.0008877551560189532</v>
       </c>
       <c r="DG191" s="398" t="n">
-        <v>0.0009421819582250272</v>
+        <v>0.0009421819582250274</v>
       </c>
     </row>
     <row r="192">
@@ -39079,10 +39079,10 @@
         <v>4099.217562323</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>355.0673848892335</v>
+        <v>355.0673848892336</v>
       </c>
       <c r="AQ192" s="179" t="n">
-        <v>303.9243496807059</v>
+        <v>303.924349680706</v>
       </c>
       <c r="AR192" s="179" t="n">
         <v>289.1790157278738</v>
@@ -39091,7 +39091,7 @@
         <v>311.5144456334122</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>342.1887372868645</v>
+        <v>342.1887372868644</v>
       </c>
       <c r="AU192" s="190" t="n">
         <v>4258.502667984552</v>
@@ -39129,10 +39129,10 @@
         <v>4099.217562323</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>355.0673848892335</v>
+        <v>355.0673848892336</v>
       </c>
       <c r="BH192" s="190" t="n">
-        <v>303.9243496807059</v>
+        <v>303.924349680706</v>
       </c>
       <c r="BI192" s="190" t="n">
         <v>289.1790157278738</v>
@@ -39141,7 +39141,7 @@
         <v>311.5144456334122</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>342.1887372868645</v>
+        <v>342.1887372868644</v>
       </c>
       <c r="BL192" s="197" t="n">
         <v>4258.502667984234</v>
@@ -39179,10 +39179,10 @@
         <v>4072.391468273</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>362.461227261988</v>
+        <v>362.4612272619881</v>
       </c>
       <c r="BY192" s="190" t="n">
-        <v>316.5837487599832</v>
+        <v>316.5837487599833</v>
       </c>
       <c r="BZ192" s="190" t="n">
         <v>306.2826859915299</v>
@@ -39191,7 +39191,7 @@
         <v>333.1365292767993</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>368.4881626721208</v>
+        <v>368.4881626721207</v>
       </c>
       <c r="CC192" s="197" t="n">
         <v>4257.209164913988</v>
@@ -39206,7 +39206,7 @@
         <v>4385.976497842799</v>
       </c>
       <c r="CG192" s="198" t="n">
-        <v>4440.879630945121</v>
+        <v>4440.87963094512</v>
       </c>
       <c r="CI192" s="197" t="n">
         <v>3805.090909090909</v>
@@ -39239,7 +39239,7 @@
         <v>1.293503069933305</v>
       </c>
       <c r="CX192" s="103" t="n">
-        <v>0.4164758392934692</v>
+        <v>0.4164758392934691</v>
       </c>
       <c r="CY192" s="103" t="n">
         <v>0.4472220454325107</v>
@@ -39251,7 +39251,7 @@
         <v>0.5266686643872664</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.003433601892741001</v>
+        <v>0.003433601892741</v>
       </c>
       <c r="DD192" s="397" t="n">
         <v>0.001204356479858206</v>
@@ -39263,7 +39263,7 @@
         <v>0.001358799154684868</v>
       </c>
       <c r="DG192" s="398" t="n">
-        <v>0.001329268013110822</v>
+        <v>0.001329268013110823</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" thickBot="1">
@@ -39391,7 +39391,7 @@
         <v>8407.126289924834</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>9470.417420962658</v>
+        <v>9470.417420962654</v>
       </c>
       <c r="AR193" s="207" t="n">
         <v>10644.94738396215</v>
@@ -39403,10 +39403,10 @@
         <v>13733.98857897227</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>9578.780758602999</v>
+        <v>9578.780758602998</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>10738.62994127602</v>
+        <v>10738.62994127601</v>
       </c>
       <c r="AW193" s="209" t="n">
         <v>12077.1659114528</v>
@@ -39441,7 +39441,7 @@
         <v>8407.126289924834</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>9470.417420962658</v>
+        <v>9470.417420962654</v>
       </c>
       <c r="BI193" s="212" t="n">
         <v>10644.94738396215</v>
@@ -39456,7 +39456,7 @@
         <v>9578.780758602834</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>10738.62994127566</v>
+        <v>10738.62994127565</v>
       </c>
       <c r="BN193" s="212" t="n">
         <v>12077.16591145315</v>
@@ -39491,31 +39491,31 @@
         <v>8061.550778031376</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>9089.514519189204</v>
+        <v>9089.514519189202</v>
       </c>
       <c r="BZ193" s="212" t="n">
-        <v>10250.41657807026</v>
+        <v>10250.41657807027</v>
       </c>
       <c r="CA193" s="212" t="n">
         <v>11615.64563397162</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>13249.17744741295</v>
+        <v>13249.17744741296</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>9213.664533961375</v>
+        <v>9213.664533961377</v>
       </c>
       <c r="CD193" s="212" t="n">
         <v>10325.0816044812</v>
       </c>
       <c r="CE193" s="212" t="n">
-        <v>11633.84335527926</v>
+        <v>11633.84335527927</v>
       </c>
       <c r="CF193" s="212" t="n">
         <v>13094.31053739562</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>14802.29343591095</v>
+        <v>14802.29343591096</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>991.6363636363636</v>
@@ -39545,34 +39545,34 @@
         <v>347856</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>365.1162246410084</v>
+        <v>365.1162246410079</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>413.5483367949305</v>
+        <v>413.5483367949299</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>443.3225561741577</v>
+        <v>443.322556174157</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>505.0503725933513</v>
+        <v>505.0503725933506</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>577.7063301463036</v>
+        <v>577.7063301463028</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0.04149604074719985</v>
       </c>
       <c r="DD193" s="423" t="n">
-        <v>0.04167148043135677</v>
+        <v>0.04167148043135678</v>
       </c>
       <c r="DE193" s="423" t="n">
-        <v>0.03962628008383994</v>
+        <v>0.03962628008383993</v>
       </c>
       <c r="DF193" s="423" t="n">
         <v>0.03980905414837371</v>
       </c>
       <c r="DG193" s="424" t="n">
-        <v>0.03989846882945772</v>
+        <v>0.03989846882945773</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" thickBot="1">
@@ -39694,25 +39694,25 @@
         <v>520446.739646707</v>
       </c>
       <c r="AO194" s="210" t="n">
-        <v>525691.6649138341</v>
+        <v>525691.664913833</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>84616.30034344189</v>
+        <v>84616.30034344184</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>79434.05362547006</v>
+        <v>79434.05362547009</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>77866.7371291983</v>
+        <v>77866.73712919829</v>
       </c>
       <c r="AS194" s="207" t="n">
-        <v>82515.14711356215</v>
+        <v>82515.14711356201</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>87032.54011691769</v>
+        <v>87032.54011691771</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>581144.1962621952</v>
+        <v>581144.1962621951</v>
       </c>
       <c r="AV194" s="207" t="n">
         <v>588243.0818146183</v>
@@ -39744,28 +39744,28 @@
         <v>520446.739646707</v>
       </c>
       <c r="BF194" s="214" t="n">
-        <v>525691.6649138341</v>
+        <v>525691.664913833</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>84616.30034344189</v>
+        <v>84616.30034344184</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>79434.05362547006</v>
+        <v>79434.05362547009</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>77866.7371291983</v>
+        <v>77866.73712919829</v>
       </c>
       <c r="BJ194" s="222" t="n">
-        <v>82515.14711356215</v>
+        <v>82515.14711356201</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>87032.54011691769</v>
+        <v>87032.54011691771</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>581144.1962621949</v>
+        <v>581144.1962621948</v>
       </c>
       <c r="BM194" s="222" t="n">
-        <v>588243.0818146181</v>
+        <v>588243.0818146182</v>
       </c>
       <c r="BN194" s="222" t="n">
         <v>595520.7883944153</v>
@@ -39774,7 +39774,7 @@
         <v>602961.8867602691</v>
       </c>
       <c r="BP194" s="214" t="n">
-        <v>612724.2050307516</v>
+        <v>612724.2050307506</v>
       </c>
       <c r="BR194" s="155" t="inlineStr">
         <is>
@@ -39794,25 +39794,25 @@
         <v>517407.811737436</v>
       </c>
       <c r="BW194" s="214" t="n">
-        <v>521990.810715448</v>
+        <v>521990.810715447</v>
       </c>
       <c r="BX194" s="221" t="n">
-        <v>85209.20506365722</v>
+        <v>85209.20506365718</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>80687.27168864106</v>
+        <v>80687.27168864111</v>
       </c>
       <c r="BZ194" s="222" t="n">
         <v>79711.60691899234</v>
       </c>
       <c r="CA194" s="222" t="n">
-        <v>84920.58215859822</v>
+        <v>84920.58215859807</v>
       </c>
       <c r="CB194" s="214" t="n">
         <v>90015.14440229512</v>
       </c>
       <c r="CC194" s="222" t="n">
-        <v>580551.5668220342</v>
+        <v>580551.5668220341</v>
       </c>
       <c r="CD194" s="222" t="n">
         <v>587708.0409090732</v>
@@ -39821,10 +39821,10 @@
         <v>594959.7541990964</v>
       </c>
       <c r="CF194" s="222" t="n">
-        <v>602328.3938960342</v>
+        <v>602328.3938960341</v>
       </c>
       <c r="CG194" s="214" t="n">
-        <v>612005.9551177432</v>
+        <v>612005.9551177422</v>
       </c>
       <c r="CI194" s="349" t="n">
         <v>485733.8181818182</v>
@@ -39854,19 +39854,19 @@
         <v>30690380.72727273</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>592.6294401595366</v>
+        <v>592.629440159536</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>535.0409055454234</v>
+        <v>535.0409055454228</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>561.0341953193961</v>
+        <v>561.0341953193953</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>633.4928642357004</v>
+        <v>633.4928642356997</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>718.2499130082971</v>
+        <v>718.2499130082963</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40651,7 +40651,7 @@
         <v>1.000000000000011</v>
       </c>
       <c r="CM198" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000009</v>
       </c>
       <c r="CN198" s="396" t="n">
         <v>1.00000000000252</v>
@@ -40663,7 +40663,7 @@
         <v>0.9999999999911314</v>
       </c>
       <c r="CQ198" s="397" t="n">
-        <v>0.9999999999961184</v>
+        <v>0.9999999999961182</v>
       </c>
       <c r="CR198" s="398" t="n">
         <v>1.00000000000709</v>
@@ -40682,7 +40682,7 @@
         <v>1.000000000000011</v>
       </c>
       <c r="CX198" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000009</v>
       </c>
       <c r="CY198" s="396" t="n">
         <v>1.002825510810508</v>
@@ -40834,22 +40834,22 @@
         <v>1549.411920748405</v>
       </c>
       <c r="AT199" s="196" t="n">
-        <v>1889.183372462288</v>
+        <v>1889.183372462287</v>
       </c>
       <c r="AU199" s="190" t="n">
         <v>54635.2999274237</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>53182.29103321584</v>
+        <v>53182.29103321586</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>52853.63355063731</v>
+        <v>52853.6335506373</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>55772.91633996381</v>
+        <v>55772.91633996365</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>58017.82774105437</v>
+        <v>58017.82774105439</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40881,25 +40881,25 @@
         <v>1225.971413171053</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>1549.411920748407</v>
+        <v>1549.411920748406</v>
       </c>
       <c r="BK199" s="198" t="n">
-        <v>1889.18337246229</v>
+        <v>1889.183372462285</v>
       </c>
       <c r="BL199" s="199" t="n">
         <v>54635.2999274237</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>53182.29103321584</v>
+        <v>53182.29103321586</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>52853.63355063731</v>
+        <v>52853.6335506373</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>55772.91633996381</v>
+        <v>55772.91633996365</v>
       </c>
       <c r="BP199" s="201" t="n">
-        <v>58017.82774105438</v>
+        <v>58017.82774105439</v>
       </c>
       <c r="BR199" s="83" t="inlineStr">
         <is>
@@ -40925,16 +40925,16 @@
         <v>0.583591731344301</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.5581738915797444</v>
+        <v>0.5581738915797442</v>
       </c>
       <c r="BZ199" s="463" t="n">
         <v>0.5345700006184666</v>
       </c>
       <c r="CA199" s="463" t="n">
-        <v>0.522382279632742</v>
+        <v>0.5223822796327436</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.5190540704828273</v>
+        <v>0.5190540704828271</v>
       </c>
       <c r="CC199" s="199" t="n">
         <v>31794.87252121307</v>
@@ -40946,7 +40946,7 @@
         <v>28202.55244808283</v>
       </c>
       <c r="CF199" s="200" t="n">
-        <v>29079.70204925467</v>
+        <v>29079.70204925468</v>
       </c>
       <c r="CG199" s="201" t="n">
         <v>30054.58263863775</v>
@@ -40970,7 +40970,7 @@
         <v>1.000000000010559</v>
       </c>
       <c r="CO199" s="397" t="n">
-        <v>0.9999999999860494</v>
+        <v>0.9999999999860495</v>
       </c>
       <c r="CP199" s="397" t="n">
         <v>0.9999999999974284</v>
@@ -41135,31 +41135,31 @@
         <v>0.00604</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>553.639838624016</v>
+        <v>553.6398386240156</v>
       </c>
       <c r="AQ200" s="190" t="n">
-        <v>831.5263981344893</v>
+        <v>831.5263981344895</v>
       </c>
       <c r="AR200" s="190" t="n">
         <v>1113.589929351027</v>
       </c>
       <c r="AS200" s="190" t="n">
-        <v>1398.867440131641</v>
+        <v>1398.867440131642</v>
       </c>
       <c r="AT200" s="196" t="n">
-        <v>1691.949533286822</v>
+        <v>1691.949533286823</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>22376.11284338876</v>
+        <v>22376.11284338871</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>18219.95848038724</v>
+        <v>18219.95848038726</v>
       </c>
       <c r="AW200" s="190" t="n">
         <v>16418.53852139305</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>17326.84046126634</v>
+        <v>17326.84046126637</v>
       </c>
       <c r="AY200" s="196" t="n">
         <v>18519.66796535328</v>
@@ -41185,10 +41185,10 @@
         <v>0.00604</v>
       </c>
       <c r="BG200" s="197" t="n">
-        <v>553.6398386240164</v>
+        <v>553.6398386240163</v>
       </c>
       <c r="BH200" s="190" t="n">
-        <v>831.5263981344893</v>
+        <v>831.5263981344895</v>
       </c>
       <c r="BI200" s="190" t="n">
         <v>1113.589929351026</v>
@@ -41200,16 +41200,16 @@
         <v>1691.94953328682</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>22376.11284338876</v>
+        <v>22376.11284338871</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>18219.95848038724</v>
+        <v>18219.95848038726</v>
       </c>
       <c r="BN200" s="190" t="n">
         <v>16418.53852139305</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>17326.84046126634</v>
+        <v>17326.84046126637</v>
       </c>
       <c r="BP200" s="198" t="n">
         <v>18519.66796535328</v>
@@ -41235,28 +41235,28 @@
         <v>5321.099802301961</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.6238389207836377</v>
+        <v>0.6238389207836391</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>0.5010147763594631</v>
+        <v>0.5010147763594625</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.3665182546622238</v>
+        <v>0.366518254662224</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.3273358126757674</v>
+        <v>0.3273358126757669</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.3152937398282328</v>
+        <v>0.3152937398282329</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>13913.99774110899</v>
       </c>
       <c r="CD200" s="190" t="n">
-        <v>9115.32806591673</v>
+        <v>9115.328065916729</v>
       </c>
       <c r="CE200" s="190" t="n">
-        <v>6009.965936352317</v>
+        <v>6009.965936352318</v>
       </c>
       <c r="CF200" s="190" t="n">
         <v>5664.325562528536</v>
@@ -41463,10 +41463,10 @@
         <v>26.82609404964608</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>363.754730331922</v>
+        <v>363.7547303319221</v>
       </c>
       <c r="AV201" s="190" t="n">
-        <v>317.0002245992777</v>
+        <v>317.0002245992778</v>
       </c>
       <c r="AW201" s="190" t="n">
         <v>306.7299080369607</v>
@@ -41475,7 +41475,7 @@
         <v>333.6222150387809</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>369.0148313365106</v>
+        <v>369.0148313365104</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41513,10 +41513,10 @@
         <v>26.82609404964358</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>363.7547303319213</v>
+        <v>363.7547303319215</v>
       </c>
       <c r="BM201" s="190" t="n">
-        <v>317.0002245992767</v>
+        <v>317.0002245992768</v>
       </c>
       <c r="BN201" s="190" t="n">
         <v>306.7299080369624</v>
@@ -41525,7 +41525,7 @@
         <v>333.6222150387784</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>369.0148313365081</v>
+        <v>369.0148313365079</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41548,10 +41548,10 @@
         <v>172.702998024501</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.6291599703816934</v>
+        <v>0.6291599703816932</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.5633013919531749</v>
+        <v>0.5633013919531746</v>
       </c>
       <c r="BZ201" s="463" t="n">
         <v>0.4928982078355731</v>
@@ -41560,10 +41560,10 @@
         <v>0.4990024760007276</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.5039930849238012</v>
+        <v>0.5039930849238015</v>
       </c>
       <c r="CC201" s="197" t="n">
-        <v>228.0460950086646</v>
+        <v>228.0460950086647</v>
       </c>
       <c r="CD201" s="190" t="n">
         <v>178.3320663462527</v>
@@ -41635,7 +41635,7 @@
         <v>1.043480180863936</v>
       </c>
       <c r="DC201" s="424" t="n">
-        <v>1.043603184610321</v>
+        <v>1.04360318461032</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1" thickBot="1">
@@ -41766,10 +41766,10 @@
         <v>32.64543502147909</v>
       </c>
       <c r="AR202" s="209" t="n">
-        <v>48.79175028226931</v>
+        <v>48.79175028226932</v>
       </c>
       <c r="AS202" s="209" t="n">
-        <v>68.54077898634314</v>
+        <v>68.54077898634316</v>
       </c>
       <c r="AT202" s="210" t="n">
         <v>92.89519858698392</v>
@@ -41778,7 +41778,7 @@
         <v>8426.667002672384</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>9503.062855984137</v>
+        <v>9503.062855984133</v>
       </c>
       <c r="AW202" s="209" t="n">
         <v>10693.73913424442</v>
@@ -41813,10 +41813,10 @@
         <v>19.54071274754978</v>
       </c>
       <c r="BH202" s="212" t="n">
-        <v>32.645435021478</v>
+        <v>32.64543502147799</v>
       </c>
       <c r="BI202" s="212" t="n">
-        <v>48.79175028227073</v>
+        <v>48.79175028227075</v>
       </c>
       <c r="BJ202" s="212" t="n">
         <v>68.54077898634267</v>
@@ -41828,7 +41828,7 @@
         <v>8426.667002672384</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>9503.062855984135</v>
+        <v>9503.062855984132</v>
       </c>
       <c r="BN202" s="212" t="n">
         <v>10693.73913424442</v>
@@ -41860,13 +41860,13 @@
         <v>9004.441202413638</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.6217306555824352</v>
+        <v>0.6217306555824353</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.626486785184136</v>
+        <v>0.6264867851841363</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.6215135643775695</v>
+        <v>0.6215135643775693</v>
       </c>
       <c r="CA202" s="467" t="n">
         <v>0.6321062005262772</v>
@@ -41875,10 +41875,10 @@
         <v>0.6406163675213075</v>
       </c>
       <c r="CC202" s="212" t="n">
-        <v>5012.113250236538</v>
+        <v>5012.113250236539</v>
       </c>
       <c r="CD202" s="212" t="n">
-        <v>5694.460730011372</v>
+        <v>5694.460730011373</v>
       </c>
       <c r="CE202" s="212" t="n">
         <v>6370.772943791379</v>
@@ -41887,7 +41887,7 @@
         <v>7342.321628349439</v>
       </c>
       <c r="CG202" s="213" t="n">
-        <v>8487.639929006915</v>
+        <v>8487.639929006917</v>
       </c>
       <c r="CW202" s="465" t="n"/>
       <c r="CX202" s="465" t="n"/>
@@ -42037,19 +42037,19 @@
         <v>3700.85419838574</v>
       </c>
       <c r="AU203" s="207" t="n">
-        <v>85801.83450381676</v>
+        <v>85801.83450381672</v>
       </c>
       <c r="AV203" s="207" t="n">
-        <v>81222.3125941865</v>
+        <v>81222.31259418653</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>80272.64111431174</v>
+        <v>80272.64111431173</v>
       </c>
       <c r="AX203" s="207" t="n">
-        <v>85554.0750228339</v>
+        <v>85554.07502283377</v>
       </c>
       <c r="AY203" s="208" t="n">
-        <v>90733.39431530342</v>
+        <v>90733.39431530343</v>
       </c>
       <c r="BA203" s="155" t="inlineStr">
         <is>
@@ -42081,25 +42081,25 @@
         <v>2405.903985113438</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>3038.927909271757</v>
+        <v>3038.927909271756</v>
       </c>
       <c r="BK203" s="214" t="n">
-        <v>3700.85419838574</v>
+        <v>3700.854198385734</v>
       </c>
       <c r="BL203" s="222" t="n">
-        <v>85801.83450381676</v>
+        <v>85801.83450381672</v>
       </c>
       <c r="BM203" s="222" t="n">
-        <v>81222.31259418649</v>
+        <v>81222.31259418653</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>80272.64111431174</v>
+        <v>80272.64111431173</v>
       </c>
       <c r="BO203" s="222" t="n">
-        <v>85554.0750228339</v>
+        <v>85554.07502283376</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>90733.39431530342</v>
+        <v>90733.39431530343</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42122,16 +42122,16 @@
         <v>43685.65694158988</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.5979287046452879</v>
+        <v>0.5979287046452881</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.5530010404475193</v>
+        <v>0.5530010404475191</v>
       </c>
       <c r="BZ203" s="467" t="n">
         <v>0.5110204032975948</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.4975541160819748</v>
+        <v>0.4975541160819758</v>
       </c>
       <c r="CB203" s="468" t="n">
         <v>0.49501954791284</v>
@@ -42146,7 +42146,7 @@
         <v>40734.25751524282</v>
       </c>
       <c r="CF203" s="212" t="n">
-        <v>42252.58519308805</v>
+        <v>42252.58519308807</v>
       </c>
       <c r="CG203" s="213" t="n">
         <v>44559.25608733314</v>
@@ -42934,7 +42934,7 @@
         <v>251650.0838085296</v>
       </c>
       <c r="AO208" s="196" t="n">
-        <v>254760.8763089937</v>
+        <v>254760.8763089927</v>
       </c>
       <c r="AP208" s="473" t="n">
         <v>0.8174081618804738</v>
@@ -42946,10 +42946,10 @@
         <v>0.8298689897704308</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.8236192334567547</v>
+        <v>0.8236192334567551</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0.8205483824767975</v>
+        <v>0.8205483824767974</v>
       </c>
       <c r="AU208" s="463" t="n">
         <v>0.8153681618804735</v>
@@ -42958,13 +42958,13 @@
         <v>0.8225332970889305</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.8258289897704315</v>
+        <v>0.8258289897704316</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.8185792334567559</v>
+        <v>0.818579233456756</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.8145083824767989</v>
+        <v>0.814508382476796</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>251650.08380853</v>
       </c>
       <c r="BF208" s="198" t="n">
-        <v>254760.876308994</v>
+        <v>254760.876308993</v>
       </c>
       <c r="BG208" s="462" t="n">
         <v>0.8174081618804737</v>
@@ -42996,10 +42996,10 @@
         <v>0.8298689897704309</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.8236192334567549</v>
+        <v>0.8236192334567554</v>
       </c>
       <c r="BK208" s="464" t="n">
-        <v>0.8205483824767978</v>
+        <v>0.8205483824767972</v>
       </c>
       <c r="BL208" s="475" t="n">
         <v>0.8153681618804725</v>
@@ -43011,10 +43011,10 @@
         <v>0.8258289897704311</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.8185792334567562</v>
+        <v>0.8185792334567566</v>
       </c>
       <c r="BP208" s="477" t="n">
-        <v>0.8145083824767988</v>
+        <v>0.8145083824767981</v>
       </c>
       <c r="BR208" s="83" t="inlineStr">
         <is>
@@ -43043,13 +43043,13 @@
         <v>0.822793715549091</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.8260908138645318</v>
+        <v>0.826090813864532</v>
       </c>
       <c r="CA208" s="463" t="n">
-        <v>0.8188600920755833</v>
+        <v>0.8188600920755839</v>
       </c>
       <c r="CB208" s="464" t="n">
-        <v>0.8148085459872298</v>
+        <v>0.8148085459872293</v>
       </c>
       <c r="CC208" s="478" t="n">
         <v>0</v>
@@ -43192,7 +43192,7 @@
         <v>261604.4269496832</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.9195906041726294</v>
+        <v>0.9195906041726296</v>
       </c>
       <c r="AQ209" s="463" t="n">
         <v>0.93642915769284</v>
@@ -43201,25 +43201,25 @@
         <v>0.9444750794865001</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>0.942612872582863</v>
+        <v>0.9426128725828629</v>
       </c>
       <c r="AT209" s="474" t="n">
         <v>0.9399276294416217</v>
       </c>
       <c r="AU209" s="463" t="n">
-        <v>0.9175506041726302</v>
+        <v>0.9175506041726308</v>
       </c>
       <c r="AV209" s="463" t="n">
-        <v>0.9333891576928401</v>
+        <v>0.9333891576928399</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.9404350794864988</v>
+        <v>0.9404350794864991</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.9375728725828626</v>
+        <v>0.9375728725828621</v>
       </c>
       <c r="AY209" s="474" t="n">
-        <v>0.9338876294416204</v>
+        <v>0.9338876294416202</v>
       </c>
       <c r="BA209" s="101" t="inlineStr">
         <is>
@@ -43242,31 +43242,31 @@
         <v>261604.426949683</v>
       </c>
       <c r="BG209" s="462" t="n">
-        <v>0.9195906041726294</v>
+        <v>0.9195906041726296</v>
       </c>
       <c r="BH209" s="463" t="n">
-        <v>0.9364291576928401</v>
+        <v>0.9364291576928399</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.9444750794864999</v>
+        <v>0.9444750794865001</v>
       </c>
       <c r="BJ209" s="463" t="n">
-        <v>0.942612872582863</v>
+        <v>0.9426128725828627</v>
       </c>
       <c r="BK209" s="464" t="n">
         <v>0.9399276294416216</v>
       </c>
       <c r="BL209" s="462" t="n">
-        <v>0.9175506041726295</v>
+        <v>0.9175506041726297</v>
       </c>
       <c r="BM209" s="463" t="n">
-        <v>0.9333891576928418</v>
+        <v>0.9333891576928417</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.9404350794865</v>
+        <v>0.9404350794865002</v>
       </c>
       <c r="BO209" s="463" t="n">
-        <v>0.9375728725828617</v>
+        <v>0.9375728725828615</v>
       </c>
       <c r="BP209" s="464" t="n">
         <v>0.933887629441621</v>
@@ -43292,13 +43292,13 @@
         <v>0</v>
       </c>
       <c r="BX209" s="462" t="n">
-        <v>0.9177950479085605</v>
+        <v>0.9177950479085607</v>
       </c>
       <c r="BY209" s="463" t="n">
         <v>0.9334786650187129</v>
       </c>
       <c r="BZ209" s="463" t="n">
-        <v>0.9405070240292105</v>
+        <v>0.9405070240292107</v>
       </c>
       <c r="CA209" s="463" t="n">
         <v>0.9376489330226312</v>
@@ -43453,7 +43453,7 @@
         <v>0.9293408640887898</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.9334345397962622</v>
+        <v>0.9334345397962621</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.928982758178619</v>
@@ -43468,7 +43468,7 @@
         <v>0.9263008640887157</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.9293945397963591</v>
+        <v>0.9293945397963589</v>
       </c>
       <c r="AX210" s="463" t="n">
         <v>0.9239427581785078</v>
@@ -43559,7 +43559,7 @@
         <v>0.9240450719604518</v>
       </c>
       <c r="CB210" s="464" t="n">
-        <v>0.9170236094434069</v>
+        <v>0.9170236094434071</v>
       </c>
       <c r="CC210" s="482" t="n">
         <v>0</v>
@@ -43702,19 +43702,19 @@
         <v>1553.115988498016</v>
       </c>
       <c r="AP211" s="489" t="n">
-        <v>0.1223177039129814</v>
+        <v>0.1223177039129813</v>
       </c>
       <c r="AQ211" s="490" t="n">
         <v>0.1180981677596262</v>
       </c>
       <c r="AR211" s="490" t="n">
-        <v>0.1185889585347563</v>
+        <v>0.1185889585347562</v>
       </c>
       <c r="AS211" s="490" t="n">
-        <v>0.1137704699986064</v>
+        <v>0.1137704699986066</v>
       </c>
       <c r="AT211" s="491" t="n">
-        <v>0.1070228356386163</v>
+        <v>0.1070228356386162</v>
       </c>
       <c r="AU211" s="490" t="n">
         <v>0.1202777039129642</v>
@@ -43755,10 +43755,10 @@
         <v>0.1223177039129663</v>
       </c>
       <c r="BH211" s="467" t="n">
-        <v>0.1180981677595966</v>
+        <v>0.1180981677595967</v>
       </c>
       <c r="BI211" s="467" t="n">
-        <v>0.118588958534782</v>
+        <v>0.1185889585347819</v>
       </c>
       <c r="BJ211" s="467" t="n">
         <v>0.1137704699986004</v>
@@ -43770,7 +43770,7 @@
         <v>0.1202777039129193</v>
       </c>
       <c r="BM211" s="467" t="n">
-        <v>0.1150581677596411</v>
+        <v>0.1150581677596412</v>
       </c>
       <c r="BN211" s="467" t="n">
         <v>0.1145489585348044</v>
@@ -43808,7 +43808,7 @@
         <v>0.1196665685194924</v>
       </c>
       <c r="BZ211" s="467" t="n">
-        <v>0.1189139938506411</v>
+        <v>0.118913993850641</v>
       </c>
       <c r="CA211" s="467" t="n">
         <v>0.1129242276026011</v>
@@ -43948,43 +43948,43 @@
         <v>507020.7692204316</v>
       </c>
       <c r="AM212" s="207" t="n">
-        <v>515248.1472801035</v>
+        <v>515248.1472801036</v>
       </c>
       <c r="AN212" s="207" t="n">
         <v>517407.8117374352</v>
       </c>
       <c r="AO212" s="208" t="n">
-        <v>521990.8107154483</v>
+        <v>521990.8107154473</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.854397065499961</v>
+        <v>0.8543970654999611</v>
       </c>
       <c r="AQ212" s="501" t="n">
         <v>0.8649638965911315</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.869245979910904</v>
+        <v>0.8692459799109039</v>
       </c>
       <c r="AS212" s="501" t="n">
         <v>0.8631503102842558</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.8579580512694948</v>
+        <v>0.8579580512694931</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.8523570654999609</v>
+        <v>0.8523570654999612</v>
       </c>
       <c r="AV212" s="501" t="n">
         <v>0.8619238965911314</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.8652059799109039</v>
+        <v>0.865205979910904</v>
       </c>
       <c r="AX212" s="501" t="n">
         <v>0.8581103102842558</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.8519180512694947</v>
+        <v>0.8519180512694932</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -43992,49 +43992,49 @@
         </is>
       </c>
       <c r="BB212" s="221" t="n">
-        <v>495342.3617583771</v>
+        <v>495342.361758377</v>
       </c>
       <c r="BC212" s="222" t="n">
         <v>507020.769220432</v>
       </c>
       <c r="BD212" s="222" t="n">
-        <v>515248.147280104</v>
+        <v>515248.1472801039</v>
       </c>
       <c r="BE212" s="222" t="n">
         <v>517407.811737436</v>
       </c>
       <c r="BF212" s="214" t="n">
-        <v>521990.8107154481</v>
+        <v>521990.810715447</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.8543970654999615</v>
+        <v>0.8543970654999616</v>
       </c>
       <c r="BH212" s="504" t="n">
-        <v>0.8649638965911318</v>
+        <v>0.8649638965911316</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.869245979910903</v>
+        <v>0.8692459799109029</v>
       </c>
       <c r="BJ212" s="504" t="n">
         <v>0.8631503102842565</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.8579580512694948</v>
+        <v>0.8579580512694945</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.8523570654999596</v>
+        <v>0.8523570654999597</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.8619238965911326</v>
+        <v>0.8619238965911323</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.8652059799109036</v>
+        <v>0.8652059799109035</v>
       </c>
       <c r="BO212" s="504" t="n">
         <v>0.8581103102842578</v>
       </c>
       <c r="BP212" s="505" t="n">
-        <v>0.8519180512694944</v>
+        <v>0.851918051269494</v>
       </c>
       <c r="BR212" s="155" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.8532271551171651</v>
+        <v>0.8532271551171653</v>
       </c>
       <c r="BY212" s="504" t="n">
         <v>0.8627085796480967</v>
@@ -44066,10 +44066,10 @@
         <v>0.8660218504589507</v>
       </c>
       <c r="CA212" s="504" t="n">
-        <v>0.8590128192209114</v>
+        <v>0.8590128192209117</v>
       </c>
       <c r="CB212" s="505" t="n">
-        <v>0.852917861910384</v>
+        <v>0.8529178619103839</v>
       </c>
       <c r="CC212" s="492" t="n">
         <v>0</v>
@@ -44737,13 +44737,13 @@
         <v>35243496.42866735</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>37683108.73025922</v>
+        <v>37683108.73025923</v>
       </c>
       <c r="AN219" s="368" t="n">
         <v>39436530.75889482</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>42660490.28941655</v>
+        <v>42660490.28941654</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>133.9987746212173</v>
@@ -44758,7 +44758,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44772,13 +44772,13 @@
         <v>35243496.42866735</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>37683108.73025922</v>
+        <v>37683108.73025923</v>
       </c>
       <c r="BE219" s="375" t="n">
         <v>39436530.75889482</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>42660490.28941655</v>
+        <v>42660490.28941654</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>133.9987746212173</v>
@@ -44793,7 +44793,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44801,19 +44801,19 @@
         </is>
       </c>
       <c r="BS219" s="391" t="n">
-        <v>32331162.05145287</v>
+        <v>32331162.05145288</v>
       </c>
       <c r="BT219" s="375" t="n">
         <v>35113719.66684505</v>
       </c>
       <c r="BU219" s="375" t="n">
-        <v>37499658.37707474</v>
+        <v>37499658.37707475</v>
       </c>
       <c r="BV219" s="375" t="n">
         <v>39195205.51180147</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>42346469.3652996</v>
+        <v>42346469.36529959</v>
       </c>
       <c r="BX219" s="386" t="n">
         <v>133.9987746212173</v>
@@ -44828,7 +44828,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="CI219" s="199" t="n">
         <v>28622673.95592171</v>
@@ -44929,7 +44929,7 @@
         <v>92524526.93696707</v>
       </c>
       <c r="AL220" s="368" t="n">
-        <v>98382120.62672204</v>
+        <v>98382120.62672202</v>
       </c>
       <c r="AM220" s="368" t="n">
         <v>102352984.8205033</v>
@@ -44938,7 +44938,7 @@
         <v>104874166.4092499</v>
       </c>
       <c r="AO220" s="380" t="n">
-        <v>108114133.9880578</v>
+        <v>108114133.9880577</v>
       </c>
       <c r="AP220" s="381" t="n">
         <v>370.7363604188515</v>
@@ -44947,10 +44947,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="AR220" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="AS220" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="AT220" s="382" t="n">
         <v>410.6176295785467</v>
@@ -44964,7 +44964,7 @@
         <v>92524526.93696707</v>
       </c>
       <c r="BC220" s="375" t="n">
-        <v>98382120.62672204</v>
+        <v>98382120.62672202</v>
       </c>
       <c r="BD220" s="375" t="n">
         <v>102352984.8205033</v>
@@ -44973,7 +44973,7 @@
         <v>104874166.4092499</v>
       </c>
       <c r="BF220" s="392" t="n">
-        <v>108114133.9880578</v>
+        <v>108114133.9880577</v>
       </c>
       <c r="BG220" s="386" t="n">
         <v>370.7363604188515</v>
@@ -44982,10 +44982,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="BI220" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="BJ220" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="BK220" s="387" t="n">
         <v>410.6176295785467</v>
@@ -44999,7 +44999,7 @@
         <v>92319272.51821274</v>
       </c>
       <c r="BT220" s="375" t="n">
-        <v>98062735.39159979</v>
+        <v>98062735.39159977</v>
       </c>
       <c r="BU220" s="375" t="n">
         <v>101915169.0774986</v>
@@ -45017,10 +45017,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="BZ220" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="CA220" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="CB220" s="387" t="n">
         <v>410.6176295785467</v>
@@ -45127,7 +45127,7 @@
         <v>1655355.268785279</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>1741275.89979978</v>
+        <v>1741275.899799779</v>
       </c>
       <c r="AN221" s="368" t="n">
         <v>1794759.152171483</v>
@@ -45139,10 +45139,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="AQ221" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="AR221" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="AS221" s="372" t="n">
         <v>440.4373424099741</v>
@@ -45162,7 +45162,7 @@
         <v>1655355.268785279</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>1741275.89979978</v>
+        <v>1741275.899799779</v>
       </c>
       <c r="BE221" s="375" t="n">
         <v>1794759.152171483</v>
@@ -45174,10 +45174,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="BH221" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="BI221" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="BJ221" s="372" t="n">
         <v>440.4373424099741</v>
@@ -45209,10 +45209,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="BY221" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="BZ221" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="CA221" s="372" t="n">
         <v>440.4373424099741</v>
@@ -45316,13 +45316,13 @@
         </is>
       </c>
       <c r="AK222" s="435" t="n">
-        <v>8344429.81823155</v>
+        <v>8344429.818231554</v>
       </c>
       <c r="AL222" s="408" t="n">
-        <v>9804168.128328595</v>
+        <v>9804168.128328592</v>
       </c>
       <c r="AM222" s="408" t="n">
-        <v>13356245.22175059</v>
+        <v>13356245.2217506</v>
       </c>
       <c r="AN222" s="408" t="n">
         <v>15497575.44785754</v>
@@ -45331,13 +45331,13 @@
         <v>17820016.2058456</v>
       </c>
       <c r="AP222" s="410" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="AQ222" s="411" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="AR222" s="411" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="AS222" s="411" t="n">
         <v>10016.49336222563</v>
@@ -45351,13 +45351,13 @@
         </is>
       </c>
       <c r="BB222" s="419" t="n">
-        <v>8344429.81823155</v>
+        <v>8344429.818231554</v>
       </c>
       <c r="BC222" s="420" t="n">
-        <v>9804168.128328595</v>
+        <v>9804168.128328592</v>
       </c>
       <c r="BD222" s="420" t="n">
-        <v>13356245.22175059</v>
+        <v>13356245.2217506</v>
       </c>
       <c r="BE222" s="420" t="n">
         <v>15497575.44785754</v>
@@ -45366,13 +45366,13 @@
         <v>17820016.2058456</v>
       </c>
       <c r="BG222" s="416" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="BH222" s="417" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="BI222" s="417" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="BJ222" s="417" t="n">
         <v>10016.49336222563</v>
@@ -45386,10 +45386,10 @@
         </is>
       </c>
       <c r="BS222" s="419" t="n">
-        <v>8205262.418214813</v>
+        <v>8205262.418214817</v>
       </c>
       <c r="BT222" s="420" t="n">
-        <v>9551796.125654062</v>
+        <v>9551796.125654057</v>
       </c>
       <c r="BU222" s="420" t="n">
         <v>12901234.64266918</v>
@@ -45401,13 +45401,13 @@
         <v>16814315.90608202</v>
       </c>
       <c r="BX222" s="416" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="BY222" s="417" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="BZ222" s="417" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="CA222" s="417" t="n">
         <v>10016.49336222563</v>
@@ -45514,7 +45514,7 @@
         <v>134803460.366449</v>
       </c>
       <c r="AL223" s="408" t="n">
-        <v>145085140.4525033</v>
+        <v>145085140.4525032</v>
       </c>
       <c r="AM223" s="408" t="n">
         <v>155133614.6723129</v>
@@ -45529,16 +45529,16 @@
         <v>271.4922192176428</v>
       </c>
       <c r="AQ223" s="437" t="n">
-        <v>285.1465528606312</v>
+        <v>285.1465528606311</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>299.6858892404014</v>
+        <v>299.6858892404015</v>
       </c>
       <c r="AS223" s="437" t="n">
         <v>310.5082988470139</v>
       </c>
       <c r="AT223" s="438" t="n">
-        <v>324.2408966014993</v>
+        <v>324.2408966014999</v>
       </c>
       <c r="BA223" s="155" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>134803460.366449</v>
       </c>
       <c r="BC223" s="440" t="n">
-        <v>145085140.4525033</v>
+        <v>145085140.4525032</v>
       </c>
       <c r="BD223" s="440" t="n">
         <v>155133614.6723129</v>
@@ -45564,16 +45564,16 @@
         <v>271.4922192176428</v>
       </c>
       <c r="BH223" s="443" t="n">
-        <v>285.1465528606312</v>
+        <v>285.1465528606311</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>299.6858892404014</v>
+        <v>299.6858892404015</v>
       </c>
       <c r="BJ223" s="443" t="n">
         <v>310.5082988470139</v>
       </c>
       <c r="BK223" s="444" t="n">
-        <v>324.2408966014993</v>
+        <v>324.2408966014999</v>
       </c>
       <c r="BR223" s="155" t="inlineStr">
         <is>
@@ -45602,13 +45602,13 @@
         <v>284.7579435124426</v>
       </c>
       <c r="BZ223" s="443" t="n">
-        <v>298.9817671161905</v>
+        <v>298.9817671161904</v>
       </c>
       <c r="CA223" s="443" t="n">
         <v>309.4361588282165</v>
       </c>
       <c r="CB223" s="444" t="n">
-        <v>322.6572597003061</v>
+        <v>322.6572597003066</v>
       </c>
       <c r="CI223" s="349" t="n">
         <v>121656683.3560072</v>
@@ -47635,13 +47635,13 @@
         <v>35243496.42866735</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>37683108.73025922</v>
+        <v>37683108.73025923</v>
       </c>
       <c r="AN237" s="368" t="n">
         <v>39436530.75889482</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>42660490.28941655</v>
+        <v>42660490.28941654</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>133.9987746212173</v>
@@ -47656,7 +47656,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47670,13 +47670,13 @@
         <v>35243496.42866735</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>37683108.73025922</v>
+        <v>37683108.73025923</v>
       </c>
       <c r="BE237" s="375" t="n">
         <v>39436530.75889482</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>42660490.28941655</v>
+        <v>42660490.28941654</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>133.9987746212173</v>
@@ -47691,7 +47691,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47699,19 +47699,19 @@
         </is>
       </c>
       <c r="BS237" s="391" t="n">
-        <v>32331162.05145287</v>
+        <v>32331162.05145288</v>
       </c>
       <c r="BT237" s="375" t="n">
         <v>35113719.66684505</v>
       </c>
       <c r="BU237" s="375" t="n">
-        <v>37499658.37707474</v>
+        <v>37499658.37707475</v>
       </c>
       <c r="BV237" s="375" t="n">
         <v>39195205.51180147</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>42346469.3652996</v>
+        <v>42346469.36529959</v>
       </c>
       <c r="BX237" s="386" t="n">
         <v>133.9987746212173</v>
@@ -47726,7 +47726,7 @@
         <v>155.7528013446777</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>166.22045731205</v>
+        <v>166.2204573120507</v>
       </c>
       <c r="CI237" s="199" t="n">
         <v>28622673.95592171</v>
@@ -47827,7 +47827,7 @@
         <v>92524526.93696707</v>
       </c>
       <c r="AL238" s="368" t="n">
-        <v>98382120.62672204</v>
+        <v>98382120.62672202</v>
       </c>
       <c r="AM238" s="368" t="n">
         <v>102352984.8205033</v>
@@ -47836,7 +47836,7 @@
         <v>104874166.4092499</v>
       </c>
       <c r="AO238" s="380" t="n">
-        <v>108114133.9880578</v>
+        <v>108114133.9880577</v>
       </c>
       <c r="AP238" s="381" t="n">
         <v>370.7363604188515</v>
@@ -47845,10 +47845,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="AR238" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="AS238" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="AT238" s="382" t="n">
         <v>410.6176295785467</v>
@@ -47862,7 +47862,7 @@
         <v>92524526.93696707</v>
       </c>
       <c r="BC238" s="375" t="n">
-        <v>98382120.62672204</v>
+        <v>98382120.62672202</v>
       </c>
       <c r="BD238" s="375" t="n">
         <v>102352984.8205033</v>
@@ -47871,7 +47871,7 @@
         <v>104874166.4092499</v>
       </c>
       <c r="BF238" s="392" t="n">
-        <v>108114133.9880578</v>
+        <v>108114133.9880577</v>
       </c>
       <c r="BG238" s="386" t="n">
         <v>370.7363604188515</v>
@@ -47880,10 +47880,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="BI238" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="BJ238" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="BK238" s="387" t="n">
         <v>410.6176295785467</v>
@@ -47897,7 +47897,7 @@
         <v>92319272.51821274</v>
       </c>
       <c r="BT238" s="375" t="n">
-        <v>98062735.39159979</v>
+        <v>98062735.39159977</v>
       </c>
       <c r="BU238" s="375" t="n">
         <v>101915169.0774986</v>
@@ -47915,10 +47915,10 @@
         <v>384.0951241463558</v>
       </c>
       <c r="BZ238" s="372" t="n">
-        <v>393.1570603012537</v>
+        <v>393.1570603012536</v>
       </c>
       <c r="CA238" s="372" t="n">
-        <v>400.8566846933713</v>
+        <v>400.8566846933712</v>
       </c>
       <c r="CB238" s="387" t="n">
         <v>410.6176295785467</v>
@@ -48025,7 +48025,7 @@
         <v>1655355.268785279</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>1741275.89979978</v>
+        <v>1741275.899799779</v>
       </c>
       <c r="AN239" s="368" t="n">
         <v>1794759.152171483</v>
@@ -48037,10 +48037,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="AQ239" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="AR239" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="AS239" s="372" t="n">
         <v>440.4373424099741</v>
@@ -48060,7 +48060,7 @@
         <v>1655355.268785279</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>1741275.89979978</v>
+        <v>1741275.899799779</v>
       </c>
       <c r="BE239" s="375" t="n">
         <v>1794759.152171483</v>
@@ -48072,10 +48072,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="BH239" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="BI239" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="BJ239" s="372" t="n">
         <v>440.4373424099741</v>
@@ -48107,10 +48107,10 @@
         <v>390.0285030454122</v>
       </c>
       <c r="BY239" s="372" t="n">
-        <v>414.1131366513682</v>
+        <v>414.1131366513683</v>
       </c>
       <c r="BZ239" s="372" t="n">
-        <v>429.4038024380909</v>
+        <v>429.4038024380908</v>
       </c>
       <c r="CA239" s="372" t="n">
         <v>440.4373424099741</v>
@@ -48214,13 +48214,13 @@
         </is>
       </c>
       <c r="AK240" s="435" t="n">
-        <v>8344429.81823155</v>
+        <v>8344429.818231554</v>
       </c>
       <c r="AL240" s="408" t="n">
-        <v>9804168.128328595</v>
+        <v>9804168.128328592</v>
       </c>
       <c r="AM240" s="408" t="n">
-        <v>13356245.22175059</v>
+        <v>13356245.2217506</v>
       </c>
       <c r="AN240" s="408" t="n">
         <v>15497575.44785754</v>
@@ -48229,13 +48229,13 @@
         <v>17820016.2058456</v>
       </c>
       <c r="AP240" s="410" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="AQ240" s="411" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="AR240" s="411" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="AS240" s="411" t="n">
         <v>10016.49336222563</v>
@@ -48249,13 +48249,13 @@
         </is>
       </c>
       <c r="BB240" s="419" t="n">
-        <v>8344429.81823155</v>
+        <v>8344429.818231554</v>
       </c>
       <c r="BC240" s="420" t="n">
-        <v>9804168.128328595</v>
+        <v>9804168.128328592</v>
       </c>
       <c r="BD240" s="420" t="n">
-        <v>13356245.22175059</v>
+        <v>13356245.2217506</v>
       </c>
       <c r="BE240" s="420" t="n">
         <v>15497575.44785754</v>
@@ -48264,13 +48264,13 @@
         <v>17820016.2058456</v>
       </c>
       <c r="BG240" s="416" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="BH240" s="417" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="BI240" s="417" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="BJ240" s="417" t="n">
         <v>10016.49336222563</v>
@@ -48284,10 +48284,10 @@
         </is>
       </c>
       <c r="BS240" s="419" t="n">
-        <v>8205262.418214813</v>
+        <v>8205262.418214817</v>
       </c>
       <c r="BT240" s="420" t="n">
-        <v>9551796.125654062</v>
+        <v>9551796.125654057</v>
       </c>
       <c r="BU240" s="420" t="n">
         <v>12901234.64266918</v>
@@ -48299,13 +48299,13 @@
         <v>16814315.90608202</v>
       </c>
       <c r="BX240" s="416" t="n">
-        <v>7121.920362448434</v>
+        <v>7121.920362448438</v>
       </c>
       <c r="BY240" s="417" t="n">
-        <v>7730.698105636812</v>
+        <v>7730.698105636809</v>
       </c>
       <c r="BZ240" s="417" t="n">
-        <v>9325.563777720732</v>
+        <v>9325.563777720734</v>
       </c>
       <c r="CA240" s="417" t="n">
         <v>10016.49336222563</v>
@@ -48412,7 +48412,7 @@
         <v>134803460.366449</v>
       </c>
       <c r="AL241" s="408" t="n">
-        <v>145085140.4525033</v>
+        <v>145085140.4525032</v>
       </c>
       <c r="AM241" s="408" t="n">
         <v>155133614.6723129</v>
@@ -48427,16 +48427,16 @@
         <v>271.4922192176428</v>
       </c>
       <c r="AQ241" s="437" t="n">
-        <v>285.1465528606312</v>
+        <v>285.1465528606311</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>299.6858892404014</v>
+        <v>299.6858892404015</v>
       </c>
       <c r="AS241" s="437" t="n">
         <v>310.5082988470139</v>
       </c>
       <c r="AT241" s="438" t="n">
-        <v>324.2408966014993</v>
+        <v>324.2408966014999</v>
       </c>
       <c r="BA241" s="155" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>134803460.366449</v>
       </c>
       <c r="BC241" s="440" t="n">
-        <v>145085140.4525033</v>
+        <v>145085140.4525032</v>
       </c>
       <c r="BD241" s="440" t="n">
         <v>155133614.6723129</v>
@@ -48462,16 +48462,16 @@
         <v>271.4922192176428</v>
       </c>
       <c r="BH241" s="443" t="n">
-        <v>285.1465528606312</v>
+        <v>285.1465528606311</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>299.6858892404014</v>
+        <v>299.6858892404015</v>
       </c>
       <c r="BJ241" s="443" t="n">
         <v>310.5082988470139</v>
       </c>
       <c r="BK241" s="444" t="n">
-        <v>324.2408966014993</v>
+        <v>324.2408966014999</v>
       </c>
       <c r="BR241" s="155" t="inlineStr">
         <is>
@@ -48500,13 +48500,13 @@
         <v>284.7579435124426</v>
       </c>
       <c r="BZ241" s="443" t="n">
-        <v>298.9817671161905</v>
+        <v>298.9817671161904</v>
       </c>
       <c r="CA241" s="443" t="n">
         <v>309.4361588282165</v>
       </c>
       <c r="CB241" s="444" t="n">
-        <v>322.6572597003061</v>
+        <v>322.6572597003066</v>
       </c>
       <c r="CI241" s="349" t="n">
         <v>121656683.3560072</v>
@@ -48966,34 +48966,34 @@
         </is>
       </c>
       <c r="C246" s="369" t="n">
-        <v>32787592.562044</v>
+        <v>32767786.992122</v>
       </c>
       <c r="D246" s="368" t="n">
-        <v>34909841.329031</v>
+        <v>34886969.337678</v>
       </c>
       <c r="E246" s="368" t="n">
-        <v>37725347.063863</v>
+        <v>37697900.67424</v>
       </c>
       <c r="F246" s="368" t="n">
-        <v>41998547.116991</v>
+        <v>41965611.449442</v>
       </c>
       <c r="G246" s="370" t="n">
-        <v>45874589.449385</v>
+        <v>45835066.648327</v>
       </c>
       <c r="H246" s="371" t="n">
-        <v>656.2462028179551</v>
+        <v>655.8497928030581</v>
       </c>
       <c r="I246" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339025</v>
       </c>
       <c r="J246" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="K246" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903365</v>
       </c>
       <c r="L246" s="373" t="n">
-        <v>875.6820672931149</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="S246" s="72" t="inlineStr">
         <is>
@@ -49001,34 +49001,34 @@
         </is>
       </c>
       <c r="T246" s="374" t="n">
-        <v>35768282.79495709</v>
+        <v>35746676.71867854</v>
       </c>
       <c r="U246" s="375" t="n">
-        <v>38083463.26803382</v>
+        <v>38058512.00473963</v>
       </c>
       <c r="V246" s="375" t="n">
-        <v>41154924.06966873</v>
+        <v>41124982.55371637</v>
       </c>
       <c r="W246" s="375" t="n">
-        <v>45816596.85489927</v>
+        <v>45780667.03575491</v>
       </c>
       <c r="X246" s="376" t="n">
-        <v>50045006.67205637</v>
+        <v>50001890.889084</v>
       </c>
       <c r="Y246" s="377" t="n">
-        <v>656.2462028179552</v>
+        <v>655.849792803058</v>
       </c>
       <c r="Z246" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339024</v>
       </c>
       <c r="AA246" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="AB246" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903366</v>
       </c>
       <c r="AC246" s="378" t="n">
-        <v>875.6820672931148</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="AJ246" s="78" t="inlineStr">
         <is>
@@ -49036,34 +49036,34 @@
         </is>
       </c>
       <c r="AK246" s="506" t="n">
-        <v>35125477.46263779</v>
+        <v>35123316.85500994</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>37283748.15044119</v>
+        <v>37281253.02411176</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>40190353.39975891</v>
+        <v>40187359.24816362</v>
       </c>
       <c r="AN246" s="368" t="n">
-        <v>44653512.4925347</v>
+        <v>44649919.51062027</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>48642442.92969159</v>
+        <v>48638131.3513944</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>650.0909759856128</v>
+        <v>650.0509881584579</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>713.274063934502</v>
+        <v>713.2263297611609</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>778.4654918664799</v>
+        <v>778.4074967632478</v>
       </c>
       <c r="AS246" s="372" t="n">
-        <v>823.5084207635792</v>
+        <v>823.4421583197751</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>866.6242250616428</v>
+        <v>866.5474090553828</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49071,34 +49071,34 @@
         </is>
       </c>
       <c r="BB246" s="391" t="n">
-        <v>35125477.46263779</v>
+        <v>35123316.85500994</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>37283748.15044119</v>
+        <v>37281253.02411176</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>40190353.39975891</v>
+        <v>40187359.24816362</v>
       </c>
       <c r="BE246" s="375" t="n">
-        <v>44653512.4925347</v>
+        <v>44649919.51062027</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>48642442.92969159</v>
+        <v>48638131.3513944</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>650.0909759856128</v>
+        <v>650.0509881584579</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>713.274063934502</v>
+        <v>713.2263297611609</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>778.4654918664799</v>
+        <v>778.4074967632478</v>
       </c>
       <c r="BJ246" s="372" t="n">
-        <v>823.5084207635792</v>
+        <v>823.4421583197751</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>866.6242250616428</v>
+        <v>866.5474090553828</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49106,34 +49106,34 @@
         </is>
       </c>
       <c r="BS246" s="391" t="n">
-        <v>35417841.95783803</v>
+        <v>35415663.36654123</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>37865895.80241719</v>
+        <v>37863361.71723823</v>
       </c>
       <c r="BU246" s="375" t="n">
-        <v>41069857.71365126</v>
+        <v>41066798.03963524</v>
       </c>
       <c r="BV246" s="375" t="n">
-        <v>45842633.7273405</v>
+        <v>45838945.06446275</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>50179799.88969613</v>
+        <v>50175352.04285435</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>650.0909759856128</v>
+        <v>650.0509881584579</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>713.274063934502</v>
+        <v>713.2263297611609</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>778.4654918664799</v>
+        <v>778.4074967632478</v>
       </c>
       <c r="CA246" s="372" t="n">
-        <v>823.5084207635792</v>
+        <v>823.4421583197751</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>866.6242250616428</v>
+        <v>866.5474090553828</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49215,31 +49215,31 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>21955923.63634825</v>
+        <v>21955923.63634826</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>19629524.31644015</v>
+        <v>19629524.31644014</v>
       </c>
       <c r="AM247" s="368" t="n">
-        <v>19653675.58159968</v>
+        <v>19653675.58159965</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>21682901.06542068</v>
+        <v>21682901.06542066</v>
       </c>
       <c r="AO247" s="380" t="n">
         <v>23759357.73670422</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>1006.115284530498</v>
+        <v>1006.115284530499</v>
       </c>
       <c r="AQ247" s="372" t="n">
         <v>1128.884089352395</v>
       </c>
       <c r="AR247" s="372" t="n">
-        <v>1284.138621139757</v>
+        <v>1284.138621139755</v>
       </c>
       <c r="AS247" s="372" t="n">
-        <v>1361.30950477185</v>
+        <v>1361.309504771849</v>
       </c>
       <c r="AT247" s="382" t="n">
         <v>1411.91795148115</v>
@@ -49250,31 +49250,31 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>21955923.63634825</v>
+        <v>21955923.63634826</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>19629524.31644015</v>
+        <v>19629524.31644014</v>
       </c>
       <c r="BD247" s="375" t="n">
-        <v>19653675.58159968</v>
+        <v>19653675.58159965</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>21682901.06542068</v>
+        <v>21682901.06542066</v>
       </c>
       <c r="BF247" s="392" t="n">
         <v>23759357.73670422</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>1006.115284530498</v>
+        <v>1006.115284530499</v>
       </c>
       <c r="BH247" s="372" t="n">
         <v>1128.884089352395</v>
       </c>
       <c r="BI247" s="372" t="n">
-        <v>1284.138621139757</v>
+        <v>1284.138621139755</v>
       </c>
       <c r="BJ247" s="372" t="n">
-        <v>1361.30950477185</v>
+        <v>1361.309504771849</v>
       </c>
       <c r="BK247" s="387" t="n">
         <v>1411.91795148115</v>
@@ -49285,31 +49285,31 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>22440225.08032641</v>
+        <v>22440225.08032642</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>20538613.44691761</v>
+        <v>20538613.44691759</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>21056602.97252256</v>
+        <v>21056602.97252252</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>23556543.24334562</v>
+        <v>23556543.24334561</v>
       </c>
       <c r="BW247" s="392" t="n">
         <v>26113244.80225675</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>1006.115284530498</v>
+        <v>1006.115284530499</v>
       </c>
       <c r="BY247" s="372" t="n">
         <v>1128.884089352395</v>
       </c>
       <c r="BZ247" s="372" t="n">
-        <v>1284.138621139757</v>
+        <v>1284.138621139755</v>
       </c>
       <c r="CA247" s="372" t="n">
-        <v>1361.30950477185</v>
+        <v>1361.309504771849</v>
       </c>
       <c r="CB247" s="387" t="n">
         <v>1411.91795148115</v>
@@ -49394,31 +49394,31 @@
         </is>
       </c>
       <c r="AK248" s="506" t="n">
-        <v>543899.1048878292</v>
+        <v>543899.104887829</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>509054.2582083818</v>
+        <v>509054.258208382</v>
       </c>
       <c r="AM248" s="368" t="n">
         <v>533269.0644891021</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>608353.1394262648</v>
+        <v>608353.1394262649</v>
       </c>
       <c r="AO248" s="380" t="n">
         <v>698752.6140111622</v>
       </c>
       <c r="AP248" s="381" t="n">
-        <v>1531.819389882462</v>
+        <v>1531.819389882461</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>1674.93739393598</v>
+        <v>1674.937393935981</v>
       </c>
       <c r="AR248" s="372" t="n">
         <v>1844.079395410529</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>1952.88901671987</v>
+        <v>1952.889016719871</v>
       </c>
       <c r="AT248" s="382" t="n">
         <v>2042.009388009476</v>
@@ -49429,31 +49429,31 @@
         </is>
       </c>
       <c r="BB248" s="391" t="n">
-        <v>543899.1048878292</v>
+        <v>543899.104887829</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>509054.2582083818</v>
+        <v>509054.258208382</v>
       </c>
       <c r="BD248" s="375" t="n">
         <v>533269.0644891021</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>608353.1394262648</v>
+        <v>608353.1394262649</v>
       </c>
       <c r="BF248" s="392" t="n">
         <v>698752.6140111622</v>
       </c>
       <c r="BG248" s="386" t="n">
-        <v>1531.819389882462</v>
+        <v>1531.819389882461</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>1674.93739393598</v>
+        <v>1674.937393935981</v>
       </c>
       <c r="BI248" s="372" t="n">
         <v>1844.079395410529</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>1952.88901671987</v>
+        <v>1952.889016719871</v>
       </c>
       <c r="BK248" s="387" t="n">
         <v>2042.009388009476</v>
@@ -49464,31 +49464,31 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>555225.1360001416</v>
+        <v>555225.1360001415</v>
       </c>
       <c r="BT248" s="375" t="n">
-        <v>530257.9591110426</v>
+        <v>530257.9591110428</v>
       </c>
       <c r="BU248" s="375" t="n">
         <v>564809.5904082197</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>650578.669091978</v>
+        <v>650578.6690919781</v>
       </c>
       <c r="BW248" s="392" t="n">
         <v>752456.2875471315</v>
       </c>
       <c r="BX248" s="386" t="n">
-        <v>1531.819389882462</v>
+        <v>1531.819389882461</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>1674.93739393598</v>
+        <v>1674.937393935981</v>
       </c>
       <c r="BZ248" s="372" t="n">
         <v>1844.079395410529</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>1952.88901671987</v>
+        <v>1952.889016719871</v>
       </c>
       <c r="CB248" s="387" t="n">
         <v>2042.009388009476</v>
@@ -49573,10 +49573,10 @@
         </is>
       </c>
       <c r="AK249" s="435" t="n">
-        <v>57217979.09779607</v>
+        <v>57217979.09779602</v>
       </c>
       <c r="AL249" s="408" t="n">
-        <v>63181982.4304093</v>
+        <v>63181982.43040927</v>
       </c>
       <c r="AM249" s="408" t="n">
         <v>68146233.1374283</v>
@@ -49585,13 +49585,13 @@
         <v>75590069.99680713</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>84448368.86548103</v>
+        <v>84448368.865481</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>6805.890279817185</v>
+        <v>6805.890279817179</v>
       </c>
       <c r="AQ249" s="411" t="n">
-        <v>6671.509778497665</v>
+        <v>6671.509778497662</v>
       </c>
       <c r="AR249" s="411" t="n">
         <v>6401.744478333399</v>
@@ -49600,7 +49600,7 @@
         <v>6271.913078569884</v>
       </c>
       <c r="AT249" s="412" t="n">
-        <v>6148.859697959794</v>
+        <v>6148.859697959792</v>
       </c>
       <c r="BA249" s="111" t="inlineStr">
         <is>
@@ -49608,10 +49608,10 @@
         </is>
       </c>
       <c r="BB249" s="419" t="n">
-        <v>57217979.09779607</v>
+        <v>57217979.09779602</v>
       </c>
       <c r="BC249" s="420" t="n">
-        <v>63181982.4304093</v>
+        <v>63181982.43040927</v>
       </c>
       <c r="BD249" s="420" t="n">
         <v>68146233.1374283</v>
@@ -49620,13 +49620,13 @@
         <v>75590069.99680713</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>84448368.86548103</v>
+        <v>84448368.865481</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>6805.890279817185</v>
+        <v>6805.890279817179</v>
       </c>
       <c r="BH249" s="417" t="n">
-        <v>6671.509778497665</v>
+        <v>6671.509778497662</v>
       </c>
       <c r="BI249" s="417" t="n">
         <v>6401.744478333399</v>
@@ -49635,7 +49635,7 @@
         <v>6271.913078569884</v>
       </c>
       <c r="BK249" s="418" t="n">
-        <v>6148.859697959794</v>
+        <v>6148.859697959792</v>
       </c>
       <c r="BR249" s="111" t="inlineStr">
         <is>
@@ -49643,13 +49643,13 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>54866030.08045748</v>
+        <v>54866030.08045744</v>
       </c>
       <c r="BT249" s="420" t="n">
-        <v>60640784.99656948</v>
+        <v>60640784.99656945</v>
       </c>
       <c r="BU249" s="420" t="n">
-        <v>65620547.72927752</v>
+        <v>65620547.72927754</v>
       </c>
       <c r="BV249" s="420" t="n">
         <v>72852319.76774202</v>
@@ -49658,10 +49658,10 @@
         <v>81467333.23751371</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>6805.890279817185</v>
+        <v>6805.890279817179</v>
       </c>
       <c r="BY249" s="417" t="n">
-        <v>6671.509778497665</v>
+        <v>6671.509778497662</v>
       </c>
       <c r="BZ249" s="417" t="n">
         <v>6401.744478333399</v>
@@ -49670,7 +49670,7 @@
         <v>6271.913078569884</v>
       </c>
       <c r="CB249" s="418" t="n">
-        <v>6148.859697959794</v>
+        <v>6148.859697959792</v>
       </c>
       <c r="CI249" s="225" t="n"/>
       <c r="CJ249" s="225" t="n"/>
@@ -49682,34 +49682,34 @@
         </is>
       </c>
       <c r="C250" s="425" t="n">
-        <v>105887411.079127</v>
+        <v>105867605.509205</v>
       </c>
       <c r="D250" s="425" t="n">
-        <v>111318078.993001</v>
+        <v>111295207.001648</v>
       </c>
       <c r="E250" s="425" t="n">
-        <v>118734694.789955</v>
+        <v>118707248.400332</v>
       </c>
       <c r="F250" s="425" t="n">
-        <v>131767816.011281</v>
+        <v>131734880.343732</v>
       </c>
       <c r="G250" s="426" t="n">
-        <v>145759194.782227</v>
+        <v>145719671.981169</v>
       </c>
       <c r="H250" s="427" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118435</v>
       </c>
       <c r="I250" s="427" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="J250" s="427" t="n">
-        <v>1648.243903578627</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="K250" s="427" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="L250" s="428" t="n">
-        <v>1805.533728250066</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="S250" s="143" t="inlineStr">
         <is>
@@ -49717,34 +49717,34 @@
         </is>
       </c>
       <c r="T250" s="429" t="n">
-        <v>115513539.3590477</v>
+        <v>115491933.2827691</v>
       </c>
       <c r="U250" s="430" t="n">
-        <v>121437904.3560011</v>
+        <v>121412953.0927069</v>
       </c>
       <c r="V250" s="430" t="n">
-        <v>129528757.9526782</v>
+        <v>129498816.4367258</v>
       </c>
       <c r="W250" s="430" t="n">
-        <v>143746708.3759429</v>
+        <v>143710778.5567985</v>
       </c>
       <c r="X250" s="431" t="n">
-        <v>159010030.6715204</v>
+        <v>158966914.888548</v>
       </c>
       <c r="Y250" s="432" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118434</v>
       </c>
       <c r="Z250" s="433" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="AA250" s="433" t="n">
-        <v>1648.243903578626</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="AB250" s="433" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="AC250" s="434" t="n">
-        <v>1805.533728250067</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="AJ250" s="150" t="inlineStr">
         <is>
@@ -49752,34 +49752,34 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>114843279.3016699</v>
+        <v>114841118.6940421</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>120604309.155499</v>
+        <v>120601814.0291695</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.0316807</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>142534836.6941888</v>
+        <v>142531243.7122743</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.5675908</v>
       </c>
       <c r="AP250" s="436" t="n">
-        <v>1357.224067177862</v>
+        <v>1357.198533000416</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>1518.294782287511</v>
+        <v>1518.263370994551</v>
       </c>
       <c r="AR250" s="437" t="n">
-        <v>1650.557554120025</v>
+        <v>1650.519101865497</v>
       </c>
       <c r="AS250" s="437" t="n">
-        <v>1727.37784128318</v>
+        <v>1727.334297981857</v>
       </c>
       <c r="AT250" s="438" t="n">
-        <v>1810.23008100466</v>
+        <v>1810.180541162534</v>
       </c>
       <c r="BA250" s="155" t="inlineStr">
         <is>
@@ -49787,34 +49787,34 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>114843279.3016699</v>
+        <v>114841118.6940421</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>120604309.155499</v>
+        <v>120601814.0291695</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.0316807</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>142534836.6941888</v>
+        <v>142531243.7122743</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.5675908</v>
       </c>
       <c r="BG250" s="442" t="n">
-        <v>1357.224067177862</v>
+        <v>1357.198533000416</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>1518.294782287511</v>
+        <v>1518.263370994551</v>
       </c>
       <c r="BI250" s="443" t="n">
-        <v>1650.557554120025</v>
+        <v>1650.519101865497</v>
       </c>
       <c r="BJ250" s="443" t="n">
-        <v>1727.37784128318</v>
+        <v>1727.334297981857</v>
       </c>
       <c r="BK250" s="444" t="n">
-        <v>1810.23008100466</v>
+        <v>1810.180541162534</v>
       </c>
       <c r="BR250" s="155" t="inlineStr">
         <is>
@@ -49822,34 +49822,34 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>113279322.2546221</v>
+        <v>113277143.6633252</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>119575552.2050153</v>
+        <v>119573018.1198363</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>128311818.0058596</v>
+        <v>128308758.3318435</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>142902075.4075201</v>
+        <v>142898386.7446423</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>158512834.2170137</v>
+        <v>158508386.3701719</v>
       </c>
       <c r="BX250" s="442" t="n">
-        <v>1329.425877990463</v>
+        <v>1329.400310432413</v>
       </c>
       <c r="BY250" s="443" t="n">
-        <v>1481.963012288187</v>
+        <v>1481.93160603134</v>
       </c>
       <c r="BZ250" s="443" t="n">
-        <v>1609.700556360106</v>
+        <v>1609.662172062834</v>
       </c>
       <c r="CA250" s="443" t="n">
-        <v>1682.773148453406</v>
+        <v>1682.729711835521</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>1760.957395219969</v>
+        <v>1760.907983014152</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51872,34 +51872,34 @@
         </is>
       </c>
       <c r="C264" s="369" t="n">
-        <v>32787592.562044</v>
+        <v>32767786.992122</v>
       </c>
       <c r="D264" s="368" t="n">
-        <v>34909841.329031</v>
+        <v>34886969.337678</v>
       </c>
       <c r="E264" s="368" t="n">
-        <v>37725347.063863</v>
+        <v>37697900.67424</v>
       </c>
       <c r="F264" s="368" t="n">
-        <v>41998547.116991</v>
+        <v>41965611.449442</v>
       </c>
       <c r="G264" s="370" t="n">
-        <v>45874589.449385</v>
+        <v>45835066.648327</v>
       </c>
       <c r="H264" s="371" t="n">
-        <v>656.2462028179551</v>
+        <v>655.8497928030581</v>
       </c>
       <c r="I264" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339025</v>
       </c>
       <c r="J264" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="K264" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903365</v>
       </c>
       <c r="L264" s="373" t="n">
-        <v>875.6820672931149</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="S264" s="72" t="inlineStr">
         <is>
@@ -51907,34 +51907,34 @@
         </is>
       </c>
       <c r="T264" s="374" t="n">
-        <v>35768282.79495709</v>
+        <v>35746676.71867854</v>
       </c>
       <c r="U264" s="375" t="n">
-        <v>38083463.26803382</v>
+        <v>38058512.00473963</v>
       </c>
       <c r="V264" s="375" t="n">
-        <v>41154924.06966873</v>
+        <v>41124982.55371637</v>
       </c>
       <c r="W264" s="375" t="n">
-        <v>45816596.85489927</v>
+        <v>45780667.03575491</v>
       </c>
       <c r="X264" s="376" t="n">
-        <v>50045006.67205637</v>
+        <v>50001890.889084</v>
       </c>
       <c r="Y264" s="377" t="n">
-        <v>656.2462028179552</v>
+        <v>655.849792803058</v>
       </c>
       <c r="Z264" s="372" t="n">
-        <v>720.4291028518486</v>
+        <v>719.9570970339024</v>
       </c>
       <c r="AA264" s="372" t="n">
-        <v>786.3483398207886</v>
+        <v>785.7762463983587</v>
       </c>
       <c r="AB264" s="372" t="n">
-        <v>831.9033709736891</v>
+        <v>831.2509842903366</v>
       </c>
       <c r="AC264" s="378" t="n">
-        <v>875.6820672931148</v>
+        <v>874.9276320262037</v>
       </c>
       <c r="AJ264" s="78" t="inlineStr">
         <is>
@@ -51942,34 +51942,34 @@
         </is>
       </c>
       <c r="AK264" s="506" t="n">
-        <v>35125477.46263779</v>
+        <v>35123316.85500994</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>37283748.15044119</v>
+        <v>37281253.02411176</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>40190353.39975891</v>
+        <v>40187359.24816362</v>
       </c>
       <c r="AN264" s="368" t="n">
-        <v>44653512.4925347</v>
+        <v>44649919.51062027</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>48642442.92969159</v>
+        <v>48638131.3513944</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>650.0909759856119</v>
+        <v>650.050988158457</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>713.2740639345028</v>
+        <v>713.2263297611613</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>778.4654918664761</v>
+        <v>778.407496763244</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>823.508420763573</v>
+        <v>823.4421583197714</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>866.6242250616416</v>
+        <v>866.5474090553812</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51977,34 +51977,34 @@
         </is>
       </c>
       <c r="BB264" s="391" t="n">
-        <v>35125477.46263779</v>
+        <v>35123316.85500994</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>37283748.15044119</v>
+        <v>37281253.02411176</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>40190353.39975891</v>
+        <v>40187359.24816362</v>
       </c>
       <c r="BE264" s="375" t="n">
-        <v>44653512.4925347</v>
+        <v>44649919.51062027</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>48642442.92969159</v>
+        <v>48638131.3513944</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>650.0909759856119</v>
+        <v>650.050988158457</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>713.2740639345028</v>
+        <v>713.2263297611613</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>778.4654918664761</v>
+        <v>778.407496763244</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>823.508420763573</v>
+        <v>823.4421583197714</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>866.6242250616416</v>
+        <v>866.5474090553812</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,34 +52012,34 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>35417841.95783802</v>
+        <v>35415663.36654123</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>37865895.80241719</v>
+        <v>37863361.71723823</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>41069857.71365126</v>
+        <v>41066798.03963524</v>
       </c>
       <c r="BV264" s="375" t="n">
-        <v>45842633.72734049</v>
+        <v>45838945.06446274</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>50179799.88969614</v>
+        <v>50175352.04285434</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>650.0909759856119</v>
+        <v>650.050988158457</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>713.2740639345028</v>
+        <v>713.2263297611613</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>778.4654918664761</v>
+        <v>778.407496763244</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>823.508420763573</v>
+        <v>823.4421583197714</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>866.6242250616416</v>
+        <v>866.5474090553812</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>1</v>
@@ -52054,22 +52054,22 @@
         <v>1.000000000000003</v>
       </c>
       <c r="CM264" s="398" t="n">
-        <v>0.9999999999999891</v>
+        <v>0.9999999999999892</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.9999999999999899</v>
+        <v>0.9999999999999857</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>0.999999999999894</v>
+        <v>0.9999999999999055</v>
       </c>
       <c r="CP264" s="103" t="n">
-        <v>1.00000000000016</v>
+        <v>1.000000000000167</v>
       </c>
       <c r="CQ264" s="103" t="n">
-        <v>1.00000000000009</v>
+        <v>1.000000000000077</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>0.9999999999998294</v>
+        <v>0.9999999999998125</v>
       </c>
       <c r="CT264" s="396" t="n">
         <v>1</v>
@@ -52084,22 +52084,22 @@
         <v>1.000000000000003</v>
       </c>
       <c r="CX264" s="398" t="n">
-        <v>0.9999999999999891</v>
+        <v>0.9999999999999892</v>
       </c>
       <c r="CY264" s="102" t="n">
-        <v>1.002825510807971</v>
+        <v>1.002825510807966</v>
       </c>
       <c r="CZ264" s="103" t="n">
-        <v>1.001786648665083</v>
+        <v>1.001786648665095</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>1.001823043211042</v>
+        <v>1.00182304321105</v>
       </c>
       <c r="DB264" s="103" t="n">
-        <v>1.001894143553857</v>
+        <v>1.001894143553844</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>1.001989946479761</v>
+        <v>1.001989946479744</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,16 +52117,16 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>23309474.00362683</v>
+        <v>23309474.00362682</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>24522422.72329472</v>
+        <v>24522422.7232947</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>26271822.68133949</v>
+        <v>26271822.68133948</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>29440637.38162252</v>
+        <v>29440637.3816225</v>
       </c>
       <c r="DO264" s="392" t="n">
         <v>32281148.46266908</v>
@@ -52209,31 +52209,31 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>21955923.63634825</v>
+        <v>21955923.63634826</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>19629524.31644015</v>
+        <v>19629524.31644014</v>
       </c>
       <c r="AM265" s="368" t="n">
-        <v>19653675.58159968</v>
+        <v>19653675.58159965</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>21682901.06542068</v>
+        <v>21682901.06542066</v>
       </c>
       <c r="AO265" s="380" t="n">
         <v>23759357.73670422</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>1006.11528453051</v>
+        <v>1006.115284530513</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>1128.884089352412</v>
+        <v>1128.88408935241</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>1284.138621139755</v>
+        <v>1284.138621139754</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>1361.309504771875</v>
+        <v>1361.309504771873</v>
       </c>
       <c r="AT265" s="382" t="n">
         <v>1411.917951481112</v>
@@ -52244,31 +52244,31 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>21955923.63634825</v>
+        <v>21955923.63634826</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>19629524.31644015</v>
+        <v>19629524.31644014</v>
       </c>
       <c r="BD265" s="375" t="n">
-        <v>19653675.58159968</v>
+        <v>19653675.58159965</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>21682901.06542068</v>
+        <v>21682901.06542066</v>
       </c>
       <c r="BF265" s="392" t="n">
         <v>23759357.73670422</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>1006.11528453051</v>
+        <v>1006.115284530513</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>1128.884089352412</v>
+        <v>1128.88408935241</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>1284.138621139755</v>
+        <v>1284.138621139754</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>1361.309504771875</v>
+        <v>1361.309504771873</v>
       </c>
       <c r="BK265" s="387" t="n">
         <v>1411.917951481112</v>
@@ -52279,31 +52279,31 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>22440225.08032641</v>
+        <v>22440225.08032642</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>20538613.44691761</v>
+        <v>20538613.44691759</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>21056602.97252256</v>
+        <v>21056602.97252253</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>23556543.24334562</v>
+        <v>23556543.24334561</v>
       </c>
       <c r="BW265" s="392" t="n">
         <v>26113244.80225675</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>1006.11528453051</v>
+        <v>1006.115284530513</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>1128.884089352412</v>
+        <v>1128.88408935241</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>1284.138621139755</v>
+        <v>1284.138621139754</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>1361.309504771875</v>
+        <v>1361.309504771873</v>
       </c>
       <c r="CB265" s="387" t="n">
         <v>1411.917951481112</v>
@@ -52324,19 +52324,19 @@
         <v>1.000000000000002</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999997787</v>
+        <v>0.9999999999997781</v>
       </c>
       <c r="CO265" s="103" t="n">
         <v>1.000000000000592</v>
       </c>
       <c r="CP265" s="103" t="n">
-        <v>1.000000000000189</v>
+        <v>1.00000000000019</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>1.000000000000648</v>
+        <v>1.000000000000649</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>1.000000000000325</v>
+        <v>1.000000000000324</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>0.9999999999999982</v>
@@ -52357,10 +52357,10 @@
         <v>1.003240790122219</v>
       </c>
       <c r="CZ265" s="103" t="n">
-        <v>1.001441567140947</v>
+        <v>1.001441567140948</v>
       </c>
       <c r="DA265" s="103" t="n">
-        <v>1.001285888588414</v>
+        <v>1.001285888588415</v>
       </c>
       <c r="DB265" s="103" t="n">
         <v>1.001301097701012</v>
@@ -52476,22 +52476,22 @@
         </is>
       </c>
       <c r="AK266" s="506" t="n">
-        <v>543899.1048878292</v>
+        <v>543899.104887829</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>509054.2582083818</v>
+        <v>509054.258208382</v>
       </c>
       <c r="AM266" s="368" t="n">
         <v>533269.0644891021</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>608353.1394262648</v>
+        <v>608353.1394262649</v>
       </c>
       <c r="AO266" s="380" t="n">
         <v>698752.6140111622</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>1531.819389881454</v>
+        <v>1531.819389881453</v>
       </c>
       <c r="AQ266" s="372" t="n">
         <v>1674.937393937601</v>
@@ -52511,22 +52511,22 @@
         </is>
       </c>
       <c r="BB266" s="391" t="n">
-        <v>543899.1048878292</v>
+        <v>543899.104887829</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>509054.2582083818</v>
+        <v>509054.258208382</v>
       </c>
       <c r="BD266" s="375" t="n">
         <v>533269.0644891021</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>608353.1394262648</v>
+        <v>608353.1394262649</v>
       </c>
       <c r="BF266" s="392" t="n">
         <v>698752.6140111622</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>1531.819389881454</v>
+        <v>1531.819389881453</v>
       </c>
       <c r="BH266" s="372" t="n">
         <v>1674.937393937601</v>
@@ -52546,10 +52546,10 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>555225.1360001416</v>
+        <v>555225.1360001415</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>530257.9591110426</v>
+        <v>530257.9591110428</v>
       </c>
       <c r="BU266" s="375" t="n">
         <v>564809.5904082197</v>
@@ -52561,7 +52561,7 @@
         <v>752456.2875471317</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>1531.819389881454</v>
+        <v>1531.819389881453</v>
       </c>
       <c r="BY266" s="372" t="n">
         <v>1674.937393937601</v>
@@ -52579,10 +52579,10 @@
         <v>1.000000000000024</v>
       </c>
       <c r="CJ266" s="397" t="n">
-        <v>0.9999999999998647</v>
+        <v>0.9999999999998646</v>
       </c>
       <c r="CK266" s="397" t="n">
-        <v>0.9999999999997061</v>
+        <v>0.9999999999997063</v>
       </c>
       <c r="CL266" s="397" t="n">
         <v>0.9999999999994522</v>
@@ -52591,16 +52591,16 @@
         <v>1.000000000000515</v>
       </c>
       <c r="CN266" s="102" t="n">
-        <v>0.9999999999946263</v>
+        <v>0.9999999999946265</v>
       </c>
       <c r="CO266" s="103" t="n">
-        <v>0.9999999999603977</v>
+        <v>0.9999999999603972</v>
       </c>
       <c r="CP266" s="103" t="n">
         <v>0.9999999999509349</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999288222</v>
+        <v>0.999999999928822</v>
       </c>
       <c r="CR266" s="104" t="n">
         <v>1.000000000054768</v>
@@ -52609,10 +52609,10 @@
         <v>1.000000000000024</v>
       </c>
       <c r="CU266" s="397" t="n">
-        <v>0.9999999999998647</v>
+        <v>0.9999999999998646</v>
       </c>
       <c r="CV266" s="397" t="n">
-        <v>0.9999999999997061</v>
+        <v>0.9999999999997063</v>
       </c>
       <c r="CW266" s="397" t="n">
         <v>0.9999999999994522</v>
@@ -52630,7 +52630,7 @@
         <v>1.001460160989883</v>
       </c>
       <c r="DB266" s="103" t="n">
-        <v>1.001457917985502</v>
+        <v>1.001457917985501</v>
       </c>
       <c r="DC266" s="104" t="n">
         <v>1.001429268938304</v>
@@ -52651,16 +52651,16 @@
         <v>0</v>
       </c>
       <c r="DK266" s="391" t="n">
-        <v>386133.3526479487</v>
+        <v>386133.3526479486</v>
       </c>
       <c r="DL266" s="375" t="n">
-        <v>355474.5971898327</v>
+        <v>355474.5971898328</v>
       </c>
       <c r="DM266" s="375" t="n">
         <v>363637.4607896128</v>
       </c>
       <c r="DN266" s="375" t="n">
-        <v>424288.0975314879</v>
+        <v>424288.0975314878</v>
       </c>
       <c r="DO266" s="392" t="n">
         <v>491540.9521924306</v>
@@ -52743,10 +52743,10 @@
         </is>
       </c>
       <c r="AK267" s="435" t="n">
-        <v>57217979.09779607</v>
+        <v>57217979.09779602</v>
       </c>
       <c r="AL267" s="408" t="n">
-        <v>63181982.4304093</v>
+        <v>63181982.43040927</v>
       </c>
       <c r="AM267" s="408" t="n">
         <v>68146233.1374283</v>
@@ -52755,22 +52755,22 @@
         <v>75590069.99680713</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>84448368.86548103</v>
+        <v>84448368.865481</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>6805.890279817319</v>
+        <v>6805.890279817314</v>
       </c>
       <c r="AQ267" s="411" t="n">
         <v>6671.509778497906</v>
       </c>
       <c r="AR267" s="411" t="n">
-        <v>6401.744478333309</v>
+        <v>6401.744478333308</v>
       </c>
       <c r="AS267" s="411" t="n">
         <v>6271.913078570079</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>6148.859697959672</v>
+        <v>6148.85969795967</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52778,10 +52778,10 @@
         </is>
       </c>
       <c r="BB267" s="419" t="n">
-        <v>57217979.09779607</v>
+        <v>57217979.09779602</v>
       </c>
       <c r="BC267" s="420" t="n">
-        <v>63181982.4304093</v>
+        <v>63181982.43040927</v>
       </c>
       <c r="BD267" s="420" t="n">
         <v>68146233.1374283</v>
@@ -52790,22 +52790,22 @@
         <v>75590069.99680713</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>84448368.86548103</v>
+        <v>84448368.865481</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>6805.890279817319</v>
+        <v>6805.890279817314</v>
       </c>
       <c r="BH267" s="417" t="n">
         <v>6671.509778497906</v>
       </c>
       <c r="BI267" s="417" t="n">
-        <v>6401.744478333309</v>
+        <v>6401.744478333308</v>
       </c>
       <c r="BJ267" s="417" t="n">
         <v>6271.913078570079</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>6148.859697959672</v>
+        <v>6148.85969795967</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52813,55 +52813,55 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>54866030.08045749</v>
+        <v>54866030.08045745</v>
       </c>
       <c r="BT267" s="420" t="n">
-        <v>60640784.99656947</v>
+        <v>60640784.99656945</v>
       </c>
       <c r="BU267" s="420" t="n">
-        <v>65620547.72927752</v>
+        <v>65620547.72927754</v>
       </c>
       <c r="BV267" s="420" t="n">
         <v>72852319.76774202</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>81467333.23751372</v>
+        <v>81467333.23751371</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>6805.890279817319</v>
+        <v>6805.890279817314</v>
       </c>
       <c r="BY267" s="417" t="n">
         <v>6671.509778497906</v>
       </c>
       <c r="BZ267" s="417" t="n">
-        <v>6401.744478333309</v>
+        <v>6401.744478333308</v>
       </c>
       <c r="CA267" s="417" t="n">
         <v>6271.913078570079</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>6148.859697959672</v>
+        <v>6148.85969795967</v>
       </c>
       <c r="CI267" s="422" t="n">
         <v>1.000000000000283</v>
       </c>
       <c r="CJ267" s="423" t="n">
-        <v>0.9999999999994664</v>
+        <v>0.9999999999994671</v>
       </c>
       <c r="CK267" s="423" t="n">
-        <v>0.9999999999996718</v>
+        <v>0.9999999999996716</v>
       </c>
       <c r="CL267" s="423" t="n">
-        <v>0.9999999999983317</v>
+        <v>0.999999999998332</v>
       </c>
       <c r="CM267" s="424" t="n">
         <v>0.9999999999997392</v>
       </c>
       <c r="CN267" s="132" t="n">
-        <v>1.000000000000402</v>
+        <v>1.000000000000403</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>1.000000000000172</v>
+        <v>1.000000000000173</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>1.000000000000147</v>
@@ -52876,25 +52876,25 @@
         <v>1.000000000000283</v>
       </c>
       <c r="CU267" s="423" t="n">
-        <v>0.9999999999994664</v>
+        <v>0.9999999999994671</v>
       </c>
       <c r="CV267" s="423" t="n">
-        <v>0.9999999999996718</v>
+        <v>0.9999999999996716</v>
       </c>
       <c r="CW267" s="423" t="n">
-        <v>0.9999999999983317</v>
+        <v>0.999999999998332</v>
       </c>
       <c r="CX267" s="424" t="n">
         <v>0.9999999999997392</v>
       </c>
       <c r="CY267" s="132" t="n">
-        <v>1.045291065539891</v>
+        <v>1.045291065539892</v>
       </c>
       <c r="CZ267" s="133" t="n">
         <v>1.045497296464163</v>
       </c>
       <c r="DA267" s="133" t="n">
-        <v>1.043249223365471</v>
+        <v>1.04324922336547</v>
       </c>
       <c r="DB267" s="133" t="n">
         <v>1.043480180827483</v>
@@ -52918,16 +52918,16 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>23375332.5545478</v>
+        <v>23375332.55454778</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>25865808.62000427</v>
+        <v>25865808.62000428</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>24844698.31488097</v>
+        <v>24844698.31488096</v>
       </c>
       <c r="DN267" s="420" t="n">
-        <v>28670741.24720098</v>
+        <v>28670741.24720095</v>
       </c>
       <c r="DO267" s="421" t="n">
         <v>33264716.15046272</v>
@@ -52940,34 +52940,34 @@
         </is>
       </c>
       <c r="C268" s="425" t="n">
-        <v>105887411.079127</v>
+        <v>105867605.509205</v>
       </c>
       <c r="D268" s="425" t="n">
-        <v>111318078.993001</v>
+        <v>111295207.001648</v>
       </c>
       <c r="E268" s="425" t="n">
-        <v>118734694.789955</v>
+        <v>118707248.400332</v>
       </c>
       <c r="F268" s="425" t="n">
-        <v>131767816.011281</v>
+        <v>131734880.343732</v>
       </c>
       <c r="G268" s="426" t="n">
-        <v>145759194.782227</v>
+        <v>145719671.981169</v>
       </c>
       <c r="H268" s="427" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118435</v>
       </c>
       <c r="I268" s="427" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="J268" s="427" t="n">
-        <v>1648.243903578627</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="K268" s="427" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="L268" s="428" t="n">
-        <v>1805.533728250066</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="S268" s="143" t="inlineStr">
         <is>
@@ -52975,34 +52975,34 @@
         </is>
       </c>
       <c r="T268" s="429" t="n">
-        <v>115513539.3590477</v>
+        <v>115491933.2827691</v>
       </c>
       <c r="U268" s="430" t="n">
-        <v>121437904.3560011</v>
+        <v>121412953.0927069</v>
       </c>
       <c r="V268" s="430" t="n">
-        <v>129528757.9526782</v>
+        <v>129498816.4367258</v>
       </c>
       <c r="W268" s="430" t="n">
-        <v>143746708.3759429</v>
+        <v>143710778.5567985</v>
       </c>
       <c r="X268" s="431" t="n">
-        <v>159010030.6715204</v>
+        <v>158966914.888548</v>
       </c>
       <c r="Y268" s="432" t="n">
-        <v>1357.453631226794</v>
+        <v>1357.199728118434</v>
       </c>
       <c r="Z268" s="433" t="n">
-        <v>1517.34088634332</v>
+        <v>1517.029125594789</v>
       </c>
       <c r="AA268" s="433" t="n">
-        <v>1648.243903578626</v>
+        <v>1647.86289999369</v>
       </c>
       <c r="AB268" s="433" t="n">
-        <v>1724.033057214062</v>
+        <v>1723.602131200907</v>
       </c>
       <c r="AC268" s="434" t="n">
-        <v>1805.533728250067</v>
+        <v>1805.044155359301</v>
       </c>
       <c r="AJ268" s="150" t="inlineStr">
         <is>
@@ -53010,34 +53010,34 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>114843279.3016699</v>
+        <v>114841118.6940421</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>120604309.155499</v>
+        <v>120601814.0291695</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.0316807</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>142534836.6941888</v>
+        <v>142531243.7122743</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.5675908</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>1357.224067177864</v>
+        <v>1357.198533000418</v>
       </c>
       <c r="AQ268" s="437" t="n">
-        <v>1518.29478228753</v>
+        <v>1518.263370994569</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>1650.557554120019</v>
+        <v>1650.519101865491</v>
       </c>
       <c r="AS268" s="437" t="n">
-        <v>1727.377841283177</v>
+        <v>1727.334297981857</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>1810.230081004646</v>
+        <v>1810.180541162519</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53045,34 +53045,34 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>114843279.3016699</v>
+        <v>114841118.6940421</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>120604309.155499</v>
+        <v>120601814.0291695</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>128523531.183276</v>
+        <v>128520537.0316807</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>142534836.6941888</v>
+        <v>142531243.7122743</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>157548922.145888</v>
+        <v>157544610.5675908</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>1357.224067177864</v>
+        <v>1357.198533000418</v>
       </c>
       <c r="BH268" s="443" t="n">
-        <v>1518.29478228753</v>
+        <v>1518.263370994569</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>1650.557554120019</v>
+        <v>1650.519101865491</v>
       </c>
       <c r="BJ268" s="443" t="n">
-        <v>1727.377841283177</v>
+        <v>1727.334297981857</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>1810.230081004646</v>
+        <v>1810.180541162519</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,34 +53080,34 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>113279322.2546221</v>
+        <v>113277143.6633252</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>119575552.2050153</v>
+        <v>119573018.1198363</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>128311818.0058596</v>
+        <v>128308758.3318435</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>142902075.4075201</v>
+        <v>142898386.7446423</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>158512834.2170137</v>
+        <v>158508386.3701719</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>1329.425877990465</v>
+        <v>1329.400310432416</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>1481.963012288205</v>
+        <v>1481.931606031357</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>1609.7005563601</v>
+        <v>1609.662172062827</v>
       </c>
       <c r="CA268" s="443" t="n">
-        <v>1682.773148453402</v>
+        <v>1682.72971183552</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>1760.957395219955</v>
+        <v>1760.907983014139</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,16 +53125,16 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>62453967.34085016</v>
+        <v>62453967.34085012</v>
       </c>
       <c r="DL268" s="440" t="n">
-        <v>63337054.60838635</v>
+        <v>63337054.60838633</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>63216662.86635345</v>
+        <v>63216662.86635342</v>
       </c>
       <c r="DN268" s="440" t="n">
-        <v>71518140.85268518</v>
+        <v>71518140.85268512</v>
       </c>
       <c r="DO268" s="441" t="n">
         <v>80360549.42928107</v>
@@ -58409,10 +58409,10 @@
         <v>153.9376778700171</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>94.8486081478395</v>
+        <v>94.84860814783953</v>
       </c>
       <c r="BZ294" s="190" t="n">
-        <v>96.17911912392225</v>
+        <v>96.17911912392221</v>
       </c>
       <c r="CA294" s="190" t="n">
         <v>105.442187320283</v>
@@ -58424,10 +58424,10 @@
         <v>153.9376778700171</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>94.8486081478395</v>
+        <v>94.84860814783953</v>
       </c>
       <c r="CE294" s="200" t="n">
-        <v>96.17911912392225</v>
+        <v>96.17911912392221</v>
       </c>
       <c r="CF294" s="200" t="n">
         <v>105.442187320283</v>
@@ -58466,10 +58466,10 @@
         <v>153.9376778700171</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>94.8486081478395</v>
+        <v>94.84860814783953</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>96.17911912392225</v>
+        <v>96.17911912392221</v>
       </c>
       <c r="CZ294" s="200" t="n">
         <v>105.442187320283</v>
@@ -58701,7 +58701,7 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>72.28203457857771</v>
+        <v>72.28203457857769</v>
       </c>
       <c r="BY295" s="190" t="n">
         <v>26.22748476335996</v>
@@ -58713,10 +58713,10 @@
         <v>22.51461856008694</v>
       </c>
       <c r="CB295" s="198" t="n">
-        <v>24.79382988119199</v>
+        <v>24.79382988119198</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>72.28203457857771</v>
+        <v>72.28203457857769</v>
       </c>
       <c r="CD295" s="190" t="n">
         <v>26.22748476335996</v>
@@ -58728,7 +58728,7 @@
         <v>22.51461856008694</v>
       </c>
       <c r="CG295" s="198" t="n">
-        <v>24.79382988119199</v>
+        <v>24.79382988119198</v>
       </c>
       <c r="CI295" s="197" t="n">
         <v>0</v>
@@ -58758,7 +58758,7 @@
         <v>0</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>72.28203457857771</v>
+        <v>72.28203457857769</v>
       </c>
       <c r="CX295" s="190" t="n">
         <v>26.22748476335996</v>
@@ -58770,7 +58770,7 @@
         <v>22.51461856008694</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>24.79382988119199</v>
+        <v>24.79382988119198</v>
       </c>
     </row>
     <row r="296">
@@ -58999,7 +58999,7 @@
         <v>1.293503069933305</v>
       </c>
       <c r="BY296" s="190" t="n">
-        <v>0.4164758392934692</v>
+        <v>0.4164758392934691</v>
       </c>
       <c r="BZ296" s="190" t="n">
         <v>0.4472220454325107</v>
@@ -59014,7 +59014,7 @@
         <v>1.293503069933305</v>
       </c>
       <c r="CD296" s="190" t="n">
-        <v>0.4164758392934692</v>
+        <v>0.4164758392934691</v>
       </c>
       <c r="CE296" s="190" t="n">
         <v>0.4472220454325107</v>
@@ -59056,7 +59056,7 @@
         <v>1.293503069933305</v>
       </c>
       <c r="CX296" s="190" t="n">
-        <v>0.4164758392934692</v>
+        <v>0.4164758392934691</v>
       </c>
       <c r="CY296" s="190" t="n">
         <v>0.4472220454325107</v>
@@ -59291,34 +59291,34 @@
         <v>0</v>
       </c>
       <c r="BX297" s="211" t="n">
-        <v>365.1162246410084</v>
+        <v>365.1162246410079</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>413.5483367949305</v>
+        <v>413.5483367949299</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>443.3225561741577</v>
+        <v>443.322556174157</v>
       </c>
       <c r="CA297" s="212" t="n">
-        <v>505.0503725933513</v>
+        <v>505.0503725933506</v>
       </c>
       <c r="CB297" s="213" t="n">
-        <v>577.7063301463036</v>
+        <v>577.7063301463028</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>365.1162246410084</v>
+        <v>365.1162246410079</v>
       </c>
       <c r="CD297" s="212" t="n">
-        <v>413.5483367949305</v>
+        <v>413.5483367949299</v>
       </c>
       <c r="CE297" s="212" t="n">
-        <v>443.3225561741577</v>
+        <v>443.322556174157</v>
       </c>
       <c r="CF297" s="212" t="n">
-        <v>505.0503725933513</v>
+        <v>505.0503725933506</v>
       </c>
       <c r="CG297" s="213" t="n">
-        <v>577.7063301463036</v>
+        <v>577.7063301463028</v>
       </c>
       <c r="CI297" s="211" t="n">
         <v>0</v>
@@ -59348,19 +59348,19 @@
         <v>0</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>365.1162246410084</v>
+        <v>365.1162246410079</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>413.5483367949305</v>
+        <v>413.5483367949299</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>443.3225561741577</v>
+        <v>443.322556174157</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>505.0503725933513</v>
+        <v>505.0503725933506</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>577.7063301463036</v>
+        <v>577.7063301463028</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59586,34 +59586,34 @@
         <v>0</v>
       </c>
       <c r="BX298" s="221" t="n">
-        <v>592.6294401595366</v>
+        <v>592.629440159536</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>535.0409055454235</v>
+        <v>535.0409055454229</v>
       </c>
       <c r="BZ298" s="222" t="n">
-        <v>561.034195319396</v>
+        <v>561.0341953193953</v>
       </c>
       <c r="CA298" s="222" t="n">
-        <v>633.4928642357004</v>
+        <v>633.4928642356997</v>
       </c>
       <c r="CB298" s="214" t="n">
-        <v>718.2499130082972</v>
+        <v>718.2499130082963</v>
       </c>
       <c r="CC298" s="222" t="n">
-        <v>592.6294401595366</v>
+        <v>592.629440159536</v>
       </c>
       <c r="CD298" s="222" t="n">
-        <v>535.0409055454235</v>
+        <v>535.0409055454229</v>
       </c>
       <c r="CE298" s="222" t="n">
-        <v>561.034195319396</v>
+        <v>561.0341953193953</v>
       </c>
       <c r="CF298" s="222" t="n">
-        <v>633.4928642357004</v>
+        <v>633.4928642356997</v>
       </c>
       <c r="CG298" s="214" t="n">
-        <v>718.2499130082972</v>
+        <v>718.2499130082963</v>
       </c>
       <c r="CI298" s="349" t="n">
         <v>0</v>
@@ -59643,19 +59643,19 @@
         <v>0</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>592.6294401595366</v>
+        <v>592.629440159536</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>535.0409055454234</v>
+        <v>535.0409055454228</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>561.0341953193961</v>
+        <v>561.0341953193953</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>633.4928642357004</v>
+        <v>633.4928642356997</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>718.2499130082971</v>
+        <v>718.2499130082963</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -71183,49 +71183,49 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>100073.4952474781</v>
+        <v>100067.3396142228</v>
       </c>
       <c r="BT368" s="375" t="n">
-        <v>67653.05219214068</v>
+        <v>67648.52467223817</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>74872.12527608851</v>
+        <v>74866.54735814614</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>86832.52916198313</v>
+        <v>86825.54230497149</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>99855.11615492479</v>
+        <v>99846.2651777586</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>650.0909759856119</v>
+        <v>650.050988158457</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>713.2740639345028</v>
+        <v>713.2263297611613</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>778.4654918664759</v>
+        <v>778.4074967632441</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>823.508420763573</v>
+        <v>823.4421583197714</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>866.6242250616417</v>
+        <v>866.5474090553812</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>100073.4952474781</v>
+        <v>100067.3396142228</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>67653.05219214068</v>
+        <v>67648.52467223817</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>74872.12527608851</v>
+        <v>74866.54735814614</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>86832.52916198313</v>
+        <v>86825.54230497149</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>99855.11615492479</v>
+        <v>99846.2651777586</v>
       </c>
     </row>
     <row r="369">
@@ -71375,49 +71375,49 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>72724.05978646986</v>
+        <v>72724.05978647005</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>29607.79025308986</v>
+        <v>29607.79025308981</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>27076.44546907204</v>
+        <v>27076.44546907201</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>30649.36424215963</v>
+        <v>30649.36424215957</v>
       </c>
       <c r="BW369" s="392" t="n">
-        <v>35006.85349522376</v>
+        <v>35006.85349522377</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1006.11528453051</v>
+        <v>1006.115284530513</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>1128.884089352412</v>
+        <v>1128.88408935241</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1284.138621139755</v>
+        <v>1284.138621139754</v>
       </c>
       <c r="CA369" s="372" t="n">
-        <v>1361.309504771875</v>
+        <v>1361.309504771873</v>
       </c>
       <c r="CB369" s="387" t="n">
         <v>1411.917951481112</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>72724.05978646986</v>
+        <v>72724.05978647005</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>29607.79025308986</v>
+        <v>29607.79025308981</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>27076.44546907204</v>
+        <v>27076.44546907201</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>30649.36424215963</v>
+        <v>30649.36424215957</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>35006.85349522376</v>
+        <v>35006.85349522377</v>
       </c>
     </row>
     <row r="370">
@@ -71567,7 +71567,7 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>1981.413083395023</v>
+        <v>1981.413083395022</v>
       </c>
       <c r="BT370" s="375" t="n">
         <v>697.5709569041784</v>
@@ -71576,13 +71576,13 @@
         <v>824.7129591558041</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>948.4903901449798</v>
+        <v>948.4903901449799</v>
       </c>
       <c r="BW370" s="392" t="n">
         <v>1075.462357049636</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>1531.819389881454</v>
+        <v>1531.819389881453</v>
       </c>
       <c r="BY370" s="372" t="n">
         <v>1674.937393937601</v>
@@ -71594,10 +71594,10 @@
         <v>1952.889016717286</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>2042.009388010285</v>
+        <v>2042.009388010286</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>1981.413083395023</v>
+        <v>1981.413083395022</v>
       </c>
       <c r="CX370" s="375" t="n">
         <v>697.5709569041784</v>
@@ -71606,7 +71606,7 @@
         <v>824.7129591558041</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>948.4903901449798</v>
+        <v>948.4903901449799</v>
       </c>
       <c r="DA370" s="392" t="n">
         <v>1075.462357049636</v>
@@ -71759,22 +71759,22 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>2484940.964287836</v>
+        <v>2484940.964287831</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>2758991.772808924</v>
+        <v>2758991.77280892</v>
       </c>
       <c r="BU371" s="420" t="n">
-        <v>2838037.726108522</v>
+        <v>2838037.726108517</v>
       </c>
       <c r="BV371" s="420" t="n">
-        <v>3167632.037204931</v>
+        <v>3167632.037204927</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>3552235.170692791</v>
+        <v>3552235.170692785</v>
       </c>
       <c r="BX371" s="416" t="n">
-        <v>6805.890279817319</v>
+        <v>6805.890279817313</v>
       </c>
       <c r="BY371" s="417" t="n">
         <v>6671.509778497906</v>
@@ -71783,25 +71783,25 @@
         <v>6401.744478333308</v>
       </c>
       <c r="CA371" s="417" t="n">
-        <v>6271.913078570078</v>
+        <v>6271.913078570079</v>
       </c>
       <c r="CB371" s="418" t="n">
-        <v>6148.859697959672</v>
+        <v>6148.85969795967</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>2484940.964287836</v>
+        <v>2484940.964287831</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>2758991.772808924</v>
+        <v>2758991.77280892</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>2838037.726108522</v>
+        <v>2838037.726108517</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>3167632.037204931</v>
+        <v>3167632.037204927</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>3552235.170692791</v>
+        <v>3552235.170692785</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71951,49 +71951,49 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>2659719.932405179</v>
+        <v>2659713.776771918</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>2856950.186211059</v>
+        <v>2856945.658691152</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>2940811.009812838</v>
+        <v>2940805.431894891</v>
       </c>
       <c r="BV372" s="440" t="n">
-        <v>3286062.420999219</v>
+        <v>3286055.434142203</v>
       </c>
       <c r="BW372" s="441" t="n">
-        <v>3688172.602699989</v>
+        <v>3688163.751722817</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>4487.998320989891</v>
+        <v>4487.987934004634</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>5339.685539180727</v>
+        <v>5339.677077173697</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>5241.767853630809</v>
+        <v>5241.757911424094</v>
       </c>
       <c r="CA372" s="443" t="n">
-        <v>5187.213000360791</v>
+        <v>5187.201971259428</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>5134.943333654652</v>
+        <v>5134.931010677639</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>2659719.932405179</v>
+        <v>2659713.776771918</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>2856950.186211059</v>
+        <v>2856945.658691152</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>2940811.009812838</v>
+        <v>2940805.431894891</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>3286062.420999219</v>
+        <v>3286055.434142203</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>3688172.602699989</v>
+        <v>3688163.751722817</v>
       </c>
     </row>
     <row r="375">
